--- a/examples/sample-report.xlsx
+++ b/examples/sample-report.xlsx
@@ -9,20 +9,22 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="AI Queries" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Regex Library" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Topic Clusters" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Opportunities" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Optimization Plan" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="AI Visibility Plan" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Method &amp; Notes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="AI Feature Pages" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Regex Library" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Topic Clusters" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Opportunities" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Optimization Plan" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="AI Visibility Plan" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Method &amp; Notes" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AI Queries'!$A$1:$R$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regex Library'!$A$4:$J$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Topic Clusters'!$A$1:$O$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Opportunities'!$A$1:$N$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Optimization Plan'!$A$1:$P$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'AI Visibility Plan'!$A$4:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AI Queries'!$A$1:$R$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AI Feature Pages'!$A$1:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Regex Library'!$A$4:$J$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Topic Clusters'!$A$1:$O$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Opportunities'!$A$1:$N$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Optimization Plan'!$A$1:$P$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'AI Visibility Plan'!$A$4:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -126,17 +128,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FEF3C7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ECFDF5"/>
       </patternFill>
     </fill>
     <fill>
@@ -214,6 +216,9 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -226,13 +231,10 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -635,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -688,7 +690,7 @@
         </is>
       </c>
       <c r="B6" s="4">
-        <f>COUNTIF('AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>COUNTIF('AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -699,7 +701,7 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -710,7 +712,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -743,7 +745,7 @@
         </is>
       </c>
       <c r="B11" s="4">
-        <f>COUNTIFS('AI Queries'!$C$2:$C$59,"Yes",'AI Queries'!$N$2:$N$59,"Yes")</f>
+        <f>COUNTIFS('AI Queries'!$C$2:$C$66,"Yes",'AI Queries'!$N$2:$N$66,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -754,7 +756,7 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTA('Topic Clusters'!$A$2:$A$11)</f>
+        <f>COUNTA('Topic Clusters'!$A$2:$A$15)</f>
         <v/>
       </c>
     </row>
@@ -765,184 +767,121 @@
         </is>
       </c>
       <c r="B13" s="4">
-        <f>SUMIFS('AI Queries'!$Q$2:$Q$59,'AI Queries'!$C$2:$C$59,"Yes")</f>
-        <v/>
+        <f>SUMIFS('AI Queries'!$Q$2:$Q$66,'AI Queries'!$C$2:$C$66,"Yes")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Impressions in Google AI features (GSC Generative AI report total)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>5400</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>The short version</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="64" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>About 7% of the site's impressions come from AI-style questions, and most land on pages that rank but don't answer the question in one quotable passage. Cost and lifespan questions already rank in the top 8, yet CTR is a fraction of what those positions earn: AI Overviews are answering them. The biggest move is answer-first blocks with real Gold Coast numbers on the cost and garage pages this week.</t>
-        </is>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>AI Mode follow-up queries (no topic word)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>AI agent / tool searches (site:, intitle:...)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
+          <t>The short version</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="64" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>About 7% of the site's impressions come from AI-style questions, and most land on pages that rank but don't answer the question in one quotable passage. Cost and lifespan questions already rank in the top 8, yet CTR is a fraction of what those positions earn: AI Overviews are answering them. The biggest move is answer-first blocks with real Gold Coast numbers on the cost and garage pages this week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
           <t>Top topics</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Topic</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>Avg position</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>Est. extra clicks</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Move</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11">
-        <f>'Topic Clusters'!B2</f>
-        <v/>
-      </c>
-      <c r="B20" s="11">
-        <f>'Topic Clusters'!C2</f>
-        <v/>
-      </c>
-      <c r="C20" s="12">
-        <f>'Topic Clusters'!F2</f>
-        <v/>
-      </c>
-      <c r="D20" s="11">
-        <f>'Topic Clusters'!E2</f>
-        <v/>
-      </c>
-      <c r="E20" s="11">
-        <f>'Topic Clusters'!H2</f>
-        <v/>
-      </c>
-      <c r="F20" s="11">
-        <f>'Topic Clusters'!K2</f>
-        <v/>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>Update existing page</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11">
-        <f>'Topic Clusters'!B3</f>
-        <v/>
-      </c>
-      <c r="B21" s="11">
-        <f>'Topic Clusters'!C3</f>
-        <v/>
-      </c>
-      <c r="C21" s="12">
-        <f>'Topic Clusters'!F3</f>
-        <v/>
-      </c>
-      <c r="D21" s="11">
-        <f>'Topic Clusters'!E3</f>
-        <v/>
-      </c>
-      <c r="E21" s="11">
-        <f>'Topic Clusters'!H3</f>
-        <v/>
-      </c>
-      <c r="F21" s="11">
-        <f>'Topic Clusters'!K3</f>
-        <v/>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Update existing page</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11">
-        <f>'Topic Clusters'!B4</f>
-        <v/>
-      </c>
-      <c r="B22" s="11">
-        <f>'Topic Clusters'!C4</f>
-        <v/>
-      </c>
-      <c r="C22" s="12">
-        <f>'Topic Clusters'!F4</f>
-        <v/>
-      </c>
-      <c r="D22" s="11">
-        <f>'Topic Clusters'!E4</f>
-        <v/>
-      </c>
-      <c r="E22" s="11">
-        <f>'Topic Clusters'!H4</f>
-        <v/>
-      </c>
-      <c r="F22" s="11">
-        <f>'Topic Clusters'!K4</f>
-        <v/>
-      </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>New section</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11">
-        <f>'Topic Clusters'!B5</f>
+        <f>'Topic Clusters'!B2</f>
         <v/>
       </c>
       <c r="B23" s="11">
-        <f>'Topic Clusters'!C5</f>
+        <f>'Topic Clusters'!C2</f>
         <v/>
       </c>
       <c r="C23" s="12">
-        <f>'Topic Clusters'!F5</f>
+        <f>'Topic Clusters'!F2</f>
         <v/>
       </c>
       <c r="D23" s="11">
-        <f>'Topic Clusters'!E5</f>
+        <f>'Topic Clusters'!E2</f>
         <v/>
       </c>
       <c r="E23" s="11">
-        <f>'Topic Clusters'!H5</f>
+        <f>'Topic Clusters'!H2</f>
         <v/>
       </c>
       <c r="F23" s="11">
-        <f>'Topic Clusters'!K5</f>
+        <f>'Topic Clusters'!K2</f>
         <v/>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -953,121 +892,214 @@
     </row>
     <row r="24">
       <c r="A24" s="11">
+        <f>'Topic Clusters'!B3</f>
+        <v/>
+      </c>
+      <c r="B24" s="11">
+        <f>'Topic Clusters'!C3</f>
+        <v/>
+      </c>
+      <c r="C24" s="12">
+        <f>'Topic Clusters'!F3</f>
+        <v/>
+      </c>
+      <c r="D24" s="11">
+        <f>'Topic Clusters'!E3</f>
+        <v/>
+      </c>
+      <c r="E24" s="11">
+        <f>'Topic Clusters'!H3</f>
+        <v/>
+      </c>
+      <c r="F24" s="11">
+        <f>'Topic Clusters'!K3</f>
+        <v/>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>Update existing page</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11">
+        <f>'Topic Clusters'!B4</f>
+        <v/>
+      </c>
+      <c r="B25" s="11">
+        <f>'Topic Clusters'!C4</f>
+        <v/>
+      </c>
+      <c r="C25" s="12">
+        <f>'Topic Clusters'!F4</f>
+        <v/>
+      </c>
+      <c r="D25" s="11">
+        <f>'Topic Clusters'!E4</f>
+        <v/>
+      </c>
+      <c r="E25" s="11">
+        <f>'Topic Clusters'!H4</f>
+        <v/>
+      </c>
+      <c r="F25" s="11">
+        <f>'Topic Clusters'!K4</f>
+        <v/>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>Update existing page</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11">
+        <f>'Topic Clusters'!B5</f>
+        <v/>
+      </c>
+      <c r="B26" s="11">
+        <f>'Topic Clusters'!C5</f>
+        <v/>
+      </c>
+      <c r="C26" s="12">
+        <f>'Topic Clusters'!F5</f>
+        <v/>
+      </c>
+      <c r="D26" s="11">
+        <f>'Topic Clusters'!E5</f>
+        <v/>
+      </c>
+      <c r="E26" s="11">
+        <f>'Topic Clusters'!H5</f>
+        <v/>
+      </c>
+      <c r="F26" s="11">
+        <f>'Topic Clusters'!K5</f>
+        <v/>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>New section</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11">
         <f>'Topic Clusters'!B6</f>
         <v/>
       </c>
-      <c r="B24" s="11">
+      <c r="B27" s="11">
         <f>'Topic Clusters'!C6</f>
         <v/>
       </c>
-      <c r="C24" s="12">
+      <c r="C27" s="12">
         <f>'Topic Clusters'!F6</f>
         <v/>
       </c>
-      <c r="D24" s="11">
+      <c r="D27" s="11">
         <f>'Topic Clusters'!E6</f>
         <v/>
       </c>
-      <c r="E24" s="11">
+      <c r="E27" s="11">
         <f>'Topic Clusters'!H6</f>
         <v/>
       </c>
-      <c r="F24" s="11">
+      <c r="F27" s="11">
         <f>'Topic Clusters'!K6</f>
         <v/>
       </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>New section</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>Update existing page</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Quick wins (days 1-7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>- Check robots.txt and the Cloudflare bot settings: allow OAI-SearchBot, ChatGPT-User, PerplexityBot, Claude-SearchBot and Bingbot</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>- Verify the site in Bing Webmaster Tools (import from GSC) and switch on IndexNow</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>- Add the T1 and T2 answer blocks + question headings to the cost and garage pages, then request indexing</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>- Rewrite the cost page title to promise the specific answer: 'Epoxy Flooring Cost Gold Coast: m² Prices + Real Jobs'</t>
+          <t>- Check robots.txt and the Cloudflare bot settings: allow OAI-SearchBot, ChatGPT-User, PerplexityBot, Claude-SearchBot and Bingbot</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
+          <t>- Verify the site in Bing Webmaster Tools (import from GSC) and switch on IndexNow</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>- Add the T1 and T2 answer blocks + question headings to the cost and garage pages, then request indexing</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>- Rewrite the cost page title to promise the specific answer: 'Epoxy Flooring Cost Gold Coast: m² Prices + Real Jobs'</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
           <t>- Save the master regex as a GSC filter and note this report's baseline (impressions, clicks, CTR)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>How to use this sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>1. Topic Clusters: what AI-style searchers want from you, biggest first.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2. Optimization Plan: the answer block, headings, FAQ and links to add per topic (green = review).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>3. AI Visibility Plan: do the quick wins this week, then the 30/90-day plan. Fill the amber cells.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4. Regex Library: save the master regex as a GSC filter and re-check monthly against this baseline.</t>
+          <t>1. Topic Clusters: what AI-style searchers want from you, biggest first.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>2. Optimization Plan: the answer block, headings, FAQ and links to add per topic (green = review).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>3. AI Visibility Plan: do the quick wins this week, then the 30/90-day plan. Fill the amber cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4. Regex Library: save the master regex as a GSC filter and re-check monthly against this baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Green cells are suggestions to review. Amber cells are yours to fill in.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>Built with ai-queries-finder by Akif Qureshi | SEO Specialist - algoblueprints.com</t>
         </is>
@@ -1075,16 +1107,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A40:G40"/>
     <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A39:G39"/>
     <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A35:G35"/>
     <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1098,7 +1130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R59"/>
+  <dimension ref="A1:R66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1398,7 +1430,7 @@
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I4" s="11" t="n">
@@ -1540,7 +1572,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I6" s="11" t="n">
@@ -1611,7 +1643,7 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I7" s="11" t="n">
@@ -1686,7 +1718,7 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I8" s="11" t="n">
@@ -1761,7 +1793,7 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="I9" s="11" t="n">
@@ -1832,7 +1864,7 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I10" s="11" t="n">
@@ -2049,7 +2081,7 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I13" s="11" t="n">
@@ -2120,7 +2152,7 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="I14" s="11" t="n">
@@ -2191,7 +2223,7 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="I15" s="11" t="n">
@@ -2337,7 +2369,7 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T9</t>
         </is>
       </c>
       <c r="I17" s="11" t="n">
@@ -2408,7 +2440,7 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>T8</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="I18" s="11" t="n">
@@ -2447,7 +2479,7 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>why is epoxy flooring so expensive</t>
+          <t>is epoxy flooring toxic once cured</t>
         </is>
       </c>
       <c r="B19" s="11">
@@ -2460,7 +2492,7 @@
         </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E19" s="17" t="inlineStr">
         <is>
@@ -2469,7 +2501,7 @@
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>R03, R09</t>
+          <t>R03</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -2479,11 +2511,11 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="I19" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>520</v>
@@ -2493,21 +2525,21 @@
         <v/>
       </c>
       <c r="L19" s="16" t="n">
-        <v>12.4</v>
+        <v>25.8</v>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>11-20</t>
+          <t>21+</t>
         </is>
       </c>
       <c r="N19" s="11" t="inlineStr"/>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>Striking distance: expand + internal links</t>
+          <t>Content gap: new section or page</t>
         </is>
       </c>
       <c r="P19" s="15" t="n">
-        <v>0.055</v>
+        <v>0.026</v>
       </c>
       <c r="Q19" s="11">
         <f>IF(H19="",0,MAX(0,ROUND(J19*P19-I19,0)))</f>
@@ -2518,7 +2550,7 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>is epoxy flooring toxic once cured</t>
+          <t>why is epoxy flooring so expensive</t>
         </is>
       </c>
       <c r="B20" s="11">
@@ -2531,7 +2563,7 @@
         </is>
       </c>
       <c r="D20" s="11" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
@@ -2540,7 +2572,7 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>R03</t>
+          <t>R03, R09</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
@@ -2550,11 +2582,11 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I20" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>520</v>
@@ -2564,21 +2596,21 @@
         <v/>
       </c>
       <c r="L20" s="16" t="n">
-        <v>25.8</v>
+        <v>12.4</v>
       </c>
       <c r="M20" s="11" t="inlineStr">
         <is>
-          <t>21+</t>
+          <t>11-20</t>
         </is>
       </c>
       <c r="N20" s="11" t="inlineStr"/>
       <c r="O20" s="11" t="inlineStr">
         <is>
-          <t>Content gap: new section or page</t>
+          <t>Striking distance: expand + internal links</t>
         </is>
       </c>
       <c r="P20" s="15" t="n">
-        <v>0.026</v>
+        <v>0.055</v>
       </c>
       <c r="Q20" s="11">
         <f>IF(H20="",0,MAX(0,ROUND(J20*P20-I20,0)))</f>
@@ -2621,7 +2653,7 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T13</t>
         </is>
       </c>
       <c r="I21" s="11" t="n">
@@ -2692,7 +2724,7 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>T9</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="I22" s="11" t="n">
@@ -2763,7 +2795,7 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T9</t>
         </is>
       </c>
       <c r="I23" s="11" t="n">
@@ -2834,7 +2866,7 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I24" s="11" t="n">
@@ -2905,7 +2937,7 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T13</t>
         </is>
       </c>
       <c r="I25" s="11" t="n">
@@ -2976,7 +3008,7 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I26" s="11" t="n">
@@ -3099,7 +3131,7 @@
         </is>
       </c>
       <c r="D28" s="11" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
@@ -3108,7 +3140,7 @@
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>R01, R03, R06</t>
+          <t>R01, R03, R06, R11</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -3118,7 +3150,7 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I28" s="11" t="n">
@@ -3189,7 +3221,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T9</t>
         </is>
       </c>
       <c r="I29" s="11" t="n">
@@ -3260,7 +3292,7 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I30" s="11" t="n">
@@ -3406,7 +3438,7 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I32" s="11" t="n">
@@ -3477,7 +3509,7 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I33" s="11" t="n">
@@ -3516,7 +3548,7 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>why is my epoxy floor peeling after one year</t>
+          <t>how thick should an epoxy garage floor be</t>
         </is>
       </c>
       <c r="B34" s="11">
@@ -3529,16 +3561,16 @@
         </is>
       </c>
       <c r="D34" s="11" t="n">
-        <v>80</v>
-      </c>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>High</t>
+        <v>45</v>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>R02, R03, R05, R09</t>
+          <t>R02, R03</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
@@ -3548,11 +3580,11 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I34" s="11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>270</v>
@@ -3562,21 +3594,21 @@
         <v/>
       </c>
       <c r="L34" s="16" t="n">
-        <v>22</v>
+        <v>9.6</v>
       </c>
       <c r="M34" s="11" t="inlineStr">
         <is>
-          <t>21+</t>
+          <t>4-10</t>
         </is>
       </c>
       <c r="N34" s="11" t="inlineStr"/>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>Content gap: new section or page</t>
+          <t>Answer upgrade</t>
         </is>
       </c>
       <c r="P34" s="15" t="n">
-        <v>0.026</v>
+        <v>0.1</v>
       </c>
       <c r="Q34" s="11">
         <f>IF(H34="",0,MAX(0,ROUND(J34*P34-I34,0)))</f>
@@ -3587,7 +3619,7 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>how thick should an epoxy garage floor be</t>
+          <t>why is my epoxy floor peeling after one year</t>
         </is>
       </c>
       <c r="B35" s="11">
@@ -3600,16 +3632,16 @@
         </is>
       </c>
       <c r="D35" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>Medium</t>
+        <v>80</v>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>R02, R03</t>
+          <t>R02, R03, R05, R09</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -3619,11 +3651,11 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I35" s="11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>270</v>
@@ -3633,21 +3665,21 @@
         <v/>
       </c>
       <c r="L35" s="16" t="n">
-        <v>9.6</v>
+        <v>22</v>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>4-10</t>
+          <t>21+</t>
         </is>
       </c>
       <c r="N35" s="11" t="inlineStr"/>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>Answer upgrade</t>
+          <t>Content gap: new section or page</t>
         </is>
       </c>
       <c r="P35" s="15" t="n">
-        <v>0.1</v>
+        <v>0.026</v>
       </c>
       <c r="Q35" s="11">
         <f>IF(H35="",0,MAX(0,ROUND(J35*P35-I35,0)))</f>
@@ -3761,7 +3793,7 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="I37" s="11" t="n">
@@ -3832,7 +3864,7 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="I38" s="11" t="n">
@@ -3903,7 +3935,7 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>T9</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="I39" s="11" t="n">
@@ -3974,7 +4006,7 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I40" s="11" t="n">
@@ -4045,7 +4077,7 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="I41" s="11" t="n">
@@ -4116,7 +4148,7 @@
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T9</t>
         </is>
       </c>
       <c r="I42" s="11" t="n">
@@ -4155,7 +4187,7 @@
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>should i choose epoxy or polished concrete for my house in a humid climate</t>
+          <t>is metallic epoxy hard to maintain</t>
         </is>
       </c>
       <c r="B43" s="11">
@@ -4168,16 +4200,16 @@
         </is>
       </c>
       <c r="D43" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>High</t>
+        <v>30</v>
+      </c>
+      <c r="E43" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>R01, R03, R05, R07, R08, R09</t>
+          <t>R03</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -4187,7 +4219,7 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>T8</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I43" s="11" t="n">
@@ -4201,7 +4233,7 @@
         <v/>
       </c>
       <c r="L43" s="16" t="n">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
@@ -4226,7 +4258,7 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>is metallic epoxy hard to maintain</t>
+          <t>should i choose epoxy or polished concrete for my house in a humid climate</t>
         </is>
       </c>
       <c r="B44" s="11">
@@ -4239,16 +4271,16 @@
         </is>
       </c>
       <c r="D44" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="E44" s="17" t="inlineStr">
-        <is>
-          <t>Medium</t>
+        <v>100</v>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>R03</t>
+          <t>R01, R03, R05, R07, R08, R09</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr">
@@ -4258,7 +4290,7 @@
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="I44" s="11" t="n">
@@ -4272,7 +4304,7 @@
         <v/>
       </c>
       <c r="L44" s="16" t="n">
-        <v>19</v>
+        <v>19.6</v>
       </c>
       <c r="M44" s="11" t="inlineStr">
         <is>
@@ -4297,7 +4329,7 @@
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>epoxy flooring cost for a 6x6 garage with crack repair included</t>
+          <t>compare epoxy flooring companies on the gold coast</t>
         </is>
       </c>
       <c r="B45" s="11">
@@ -4310,26 +4342,26 @@
         </is>
       </c>
       <c r="D45" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="E45" s="17" t="inlineStr">
-        <is>
-          <t>Medium</t>
+        <v>60</v>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02, R04, R06</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="I45" s="11" t="n">
@@ -4343,7 +4375,7 @@
         <v/>
       </c>
       <c r="L45" s="16" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
@@ -4368,7 +4400,7 @@
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>compare epoxy flooring companies on the gold coast</t>
+          <t>epoxy flooring cost for a 6x6 garage with crack repair included</t>
         </is>
       </c>
       <c r="B46" s="11">
@@ -4381,26 +4413,26 @@
         </is>
       </c>
       <c r="D46" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="E46" s="14" t="inlineStr">
-        <is>
-          <t>High</t>
+        <v>35</v>
+      </c>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>R02, R04, R06</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I46" s="11" t="n">
@@ -4414,7 +4446,7 @@
         <v/>
       </c>
       <c r="L46" s="16" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M46" s="11" t="inlineStr">
         <is>
@@ -4471,7 +4503,7 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I47" s="11" t="n">
@@ -4523,7 +4555,7 @@
         </is>
       </c>
       <c r="D48" s="11" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
@@ -4532,7 +4564,7 @@
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>R01, R04, R05, R08</t>
+          <t>R01, R04, R08</t>
         </is>
       </c>
       <c r="G48" s="11" t="inlineStr">
@@ -4542,7 +4574,7 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I48" s="11" t="n">
@@ -4613,7 +4645,7 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I49" s="11" t="n">
@@ -4684,7 +4716,7 @@
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="I50" s="11" t="n">
@@ -4755,7 +4787,7 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I51" s="11" t="n">
@@ -4897,7 +4929,7 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I53" s="11" t="n">
@@ -4968,7 +5000,7 @@
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="I54" s="11" t="n">
@@ -5039,7 +5071,7 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I55" s="11" t="n">
@@ -5145,7 +5177,7 @@
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>is coastline epoxy any good</t>
+          <t>show me photos</t>
         </is>
       </c>
       <c r="B57" s="11">
@@ -5158,36 +5190,40 @@
         </is>
       </c>
       <c r="D57" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="E57" s="17" t="inlineStr">
-        <is>
-          <t>Medium</t>
+        <v>60</v>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>R03</t>
+          <t>R04, R11</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="H57" s="11" t="inlineStr"/>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
       <c r="I57" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K57" s="15">
         <f>IF(J57&gt;0,I57/J57,0)</f>
         <v/>
       </c>
       <c r="L57" s="16" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
@@ -5212,7 +5248,7 @@
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>my garage floor</t>
+          <t>is coastline epoxy any good</t>
         </is>
       </c>
       <c r="B58" s="11">
@@ -5221,54 +5257,54 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D58" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="E58" s="18" t="inlineStr">
-        <is>
-          <t>Low</t>
+        <v>30</v>
+      </c>
+      <c r="E58" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>R05</t>
+          <t>R03</t>
         </is>
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr"/>
       <c r="I58" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="K58" s="15">
         <f>IF(J58&gt;0,I58/J58,0)</f>
         <v/>
       </c>
       <c r="L58" s="16" t="n">
-        <v>34</v>
+        <v>1.2</v>
       </c>
       <c r="M58" s="11" t="inlineStr">
         <is>
-          <t>21+</t>
+          <t>Top 3</t>
         </is>
       </c>
       <c r="N58" s="11" t="inlineStr"/>
       <c r="O58" s="11" t="inlineStr">
         <is>
-          <t>Content gap: new section or page</t>
+          <t>Defend &amp; get cited</t>
         </is>
       </c>
       <c r="P58" s="15" t="n">
-        <v>0.026</v>
+        <v>0.25</v>
       </c>
       <c r="Q58" s="11">
         <f>IF(H58="",0,MAX(0,ROUND(J58*P58-I58,0)))</f>
@@ -5279,7 +5315,7 @@
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>our flooring options</t>
+          <t>which is cheaper?</t>
         </is>
       </c>
       <c r="B59" s="11">
@@ -5288,20 +5324,20 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D59" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="E59" s="18" t="inlineStr">
-        <is>
-          <t>Low</t>
+        <v>60</v>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>R05</t>
+          <t>R03, R11</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -5309,33 +5345,37 @@
           <t>Informational</t>
         </is>
       </c>
-      <c r="H59" s="11" t="inlineStr"/>
+      <c r="H59" s="11" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
       <c r="I59" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K59" s="15">
         <f>IF(J59&gt;0,I59/J59,0)</f>
         <v/>
       </c>
       <c r="L59" s="16" t="n">
-        <v>45</v>
+        <v>3.5</v>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>21+</t>
+          <t>4-10</t>
         </is>
       </c>
       <c r="N59" s="11" t="inlineStr"/>
       <c r="O59" s="11" t="inlineStr">
         <is>
-          <t>Content gap: new section or page</t>
+          <t>Answer upgrade</t>
         </is>
       </c>
       <c r="P59" s="15" t="n">
-        <v>0.026</v>
+        <v>0.1</v>
       </c>
       <c r="Q59" s="11">
         <f>IF(H59="",0,MAX(0,ROUND(J59*P59-I59,0)))</f>
@@ -5343,9 +5383,498 @@
       </c>
       <c r="R59" s="11" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>show me photos of flake vs metallic</t>
+        </is>
+      </c>
+      <c r="B60" s="11">
+        <f>IF(LEN(TRIM(A60))=0,0,LEN(TRIM(A60))-LEN(SUBSTITUTE(TRIM(A60)," ",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>R02, R04, R06, R11</t>
+        </is>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J60" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K60" s="15">
+        <f>IF(J60&gt;0,I60/J60,0)</f>
+        <v/>
+      </c>
+      <c r="L60" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M60" s="11" t="inlineStr">
+        <is>
+          <t>Top 3</t>
+        </is>
+      </c>
+      <c r="N60" s="11" t="inlineStr"/>
+      <c r="O60" s="11" t="inlineStr">
+        <is>
+          <t>Defend &amp; get cited</t>
+        </is>
+      </c>
+      <c r="P60" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q60" s="11">
+        <f>IF(H60="",0,MAX(0,ROUND(J60*P60-I60,0)))</f>
+        <v/>
+      </c>
+      <c r="R60" s="11" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>how about in brisbane</t>
+        </is>
+      </c>
+      <c r="B61" s="11">
+        <f>IF(LEN(TRIM(A61))=0,0,LEN(TRIM(A61))-LEN(SUBSTITUTE(TRIM(A61)," ",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="E61" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>R03, R11</t>
+        </is>
+      </c>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J61" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="K61" s="15">
+        <f>IF(J61&gt;0,I61/J61,0)</f>
+        <v/>
+      </c>
+      <c r="L61" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M61" s="11" t="inlineStr">
+        <is>
+          <t>4-10</t>
+        </is>
+      </c>
+      <c r="N61" s="11" t="inlineStr"/>
+      <c r="O61" s="11" t="inlineStr">
+        <is>
+          <t>Answer upgrade</t>
+        </is>
+      </c>
+      <c r="P61" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q61" s="11">
+        <f>IF(H61="",0,MAX(0,ROUND(J61*P61-I61,0)))</f>
+        <v/>
+      </c>
+      <c r="R61" s="11" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>are they slippery</t>
+        </is>
+      </c>
+      <c r="B62" s="11">
+        <f>IF(LEN(TRIM(A62))=0,0,LEN(TRIM(A62))-LEN(SUBSTITUTE(TRIM(A62)," ",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="E62" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>R03, R11</t>
+        </is>
+      </c>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="K62" s="15">
+        <f>IF(J62&gt;0,I62/J62,0)</f>
+        <v/>
+      </c>
+      <c r="L62" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M62" s="11" t="inlineStr">
+        <is>
+          <t>Top 3</t>
+        </is>
+      </c>
+      <c r="N62" s="11" t="inlineStr"/>
+      <c r="O62" s="11" t="inlineStr">
+        <is>
+          <t>Defend &amp; get cited</t>
+        </is>
+      </c>
+      <c r="P62" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q62" s="11">
+        <f>IF(H62="",0,MAX(0,ROUND(J62*P62-I62,0)))</f>
+        <v/>
+      </c>
+      <c r="R62" s="11" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>"epoxy flooring" -site:reddit.com -site:youtube.com</t>
+        </is>
+      </c>
+      <c r="B63" s="11">
+        <f>IF(LEN(TRIM(A63))=0,0,LEN(TRIM(A63))-LEN(SUBSTITUTE(TRIM(A63)," ",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="E63" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H63" s="11" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K63" s="15">
+        <f>IF(J63&gt;0,I63/J63,0)</f>
+        <v/>
+      </c>
+      <c r="L63" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M63" s="11" t="inlineStr">
+        <is>
+          <t>4-10</t>
+        </is>
+      </c>
+      <c r="N63" s="11" t="inlineStr"/>
+      <c r="O63" s="11" t="inlineStr">
+        <is>
+          <t>None: AI agent / tool search</t>
+        </is>
+      </c>
+      <c r="P63" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="11">
+        <f>IF(H63="",0,MAX(0,ROUND(J63*P63-I63,0)))</f>
+        <v/>
+      </c>
+      <c r="R63" s="11" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>site:gov.au epoxy fumes ventilation</t>
+        </is>
+      </c>
+      <c r="B64" s="11">
+        <f>IF(LEN(TRIM(A64))=0,0,LEN(TRIM(A64))-LEN(SUBSTITUTE(TRIM(A64)," ",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K64" s="15">
+        <f>IF(J64&gt;0,I64/J64,0)</f>
+        <v/>
+      </c>
+      <c r="L64" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="M64" s="11" t="inlineStr">
+        <is>
+          <t>4-10</t>
+        </is>
+      </c>
+      <c r="N64" s="11" t="inlineStr"/>
+      <c r="O64" s="11" t="inlineStr">
+        <is>
+          <t>None: AI agent / tool search</t>
+        </is>
+      </c>
+      <c r="P64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="11">
+        <f>IF(H64="",0,MAX(0,ROUND(J64*P64-I64,0)))</f>
+        <v/>
+      </c>
+      <c r="R64" s="11" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>my garage floor</t>
+        </is>
+      </c>
+      <c r="B65" s="11">
+        <f>IF(LEN(TRIM(A65))=0,0,LEN(TRIM(A65))-LEN(SUBSTITUTE(TRIM(A65)," ",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E65" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>R05</t>
+        </is>
+      </c>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H65" s="11" t="inlineStr"/>
+      <c r="I65" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="K65" s="15">
+        <f>IF(J65&gt;0,I65/J65,0)</f>
+        <v/>
+      </c>
+      <c r="L65" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="M65" s="11" t="inlineStr">
+        <is>
+          <t>21+</t>
+        </is>
+      </c>
+      <c r="N65" s="11" t="inlineStr"/>
+      <c r="O65" s="11" t="inlineStr">
+        <is>
+          <t>Content gap: new section or page</t>
+        </is>
+      </c>
+      <c r="P65" s="15" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="Q65" s="11">
+        <f>IF(H65="",0,MAX(0,ROUND(J65*P65-I65,0)))</f>
+        <v/>
+      </c>
+      <c r="R65" s="11" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>our flooring options</t>
+        </is>
+      </c>
+      <c r="B66" s="11">
+        <f>IF(LEN(TRIM(A66))=0,0,LEN(TRIM(A66))-LEN(SUBSTITUTE(TRIM(A66)," ",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E66" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>R05</t>
+        </is>
+      </c>
+      <c r="G66" s="11" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H66" s="11" t="inlineStr"/>
+      <c r="I66" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K66" s="15">
+        <f>IF(J66&gt;0,I66/J66,0)</f>
+        <v/>
+      </c>
+      <c r="L66" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="M66" s="11" t="inlineStr">
+        <is>
+          <t>21+</t>
+        </is>
+      </c>
+      <c r="N66" s="11" t="inlineStr"/>
+      <c r="O66" s="11" t="inlineStr">
+        <is>
+          <t>Content gap: new section or page</t>
+        </is>
+      </c>
+      <c r="P66" s="15" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="Q66" s="11">
+        <f>IF(H66="",0,MAX(0,ROUND(J66*P66-I66,0)))</f>
+        <v/>
+      </c>
+      <c r="R66" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R59"/>
-  <conditionalFormatting sqref="D2:D59">
+  <autoFilter ref="A1:R66"/>
+  <conditionalFormatting sqref="D2:D66">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5355,7 +5884,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N59">
+  <conditionalFormatting sqref="N2:N66">
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
       <formula>"Yes"</formula>
     </cfRule>
@@ -5371,7 +5900,401 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>AI feature impressions</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Share of AI impressions</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Search impressions</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>Avg position</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>AI share of page impressions</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/epoxy-garage-floors/</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="n">
+        <v>1560</v>
+      </c>
+      <c r="D2" s="15">
+        <f>IF(SUM($C$2:$C$9)&gt;0,C2/SUM($C$2:$C$9),0)</f>
+        <v/>
+      </c>
+      <c r="E2" s="12" t="n">
+        <v>5200</v>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>62</v>
+      </c>
+      <c r="G2" s="15">
+        <f>IF(N(E2)&gt;0,F2/E2,"")</f>
+        <v/>
+      </c>
+      <c r="H2" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I2" s="15">
+        <f>IF(N(E2)&gt;0,C2/E2,"")</f>
+        <v/>
+      </c>
+      <c r="J2" s="19" t="inlineStr">
+        <is>
+          <t>Most AI-shown page (1,560). Lead with the lifespan and 'is it worth it' answers (T2, T4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/flake-epoxy-flooring/</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="n">
+        <v>1189</v>
+      </c>
+      <c r="D3" s="15">
+        <f>IF(SUM($C$2:$C$9)&gt;0,C3/SUM($C$2:$C$9),0)</f>
+        <v/>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>2900</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="G3" s="15">
+        <f>IF(N(E3)&gt;0,F3/E3,"")</f>
+        <v/>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" s="15">
+        <f>IF(N(E3)&gt;0,C3/E3,"")</f>
+        <v/>
+      </c>
+      <c r="J3" s="19" t="inlineStr">
+        <is>
+          <t>41% of its impressions are AI features. Add the definition block (T5) and the photo gallery (T12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/epoxy-flooring-cost/</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>1066</v>
+      </c>
+      <c r="D4" s="15">
+        <f>IF(SUM($C$2:$C$9)&gt;0,C4/SUM($C$2:$C$9),0)</f>
+        <v/>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>4100</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>49</v>
+      </c>
+      <c r="G4" s="15">
+        <f>IF(N(E4)&gt;0,F4/E4,"")</f>
+        <v/>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I4" s="15">
+        <f>IF(N(E4)&gt;0,C4/E4,"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>1,066 AI impressions. Answer block + cost table at the top (T1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/blog/how-to-clean-epoxy-floors/</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>646</v>
+      </c>
+      <c r="D5" s="15">
+        <f>IF(SUM($C$2:$C$9)&gt;0,C5/SUM($C$2:$C$9),0)</f>
+        <v/>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="G5" s="15">
+        <f>IF(N(E5)&gt;0,F5/E5,"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" s="15">
+        <f>IF(N(E5)&gt;0,C5/E5,"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="19" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr"/>
+      <c r="C6" s="12" t="n">
+        <v>620</v>
+      </c>
+      <c r="D6" s="15">
+        <f>IF(SUM($C$2:$C$9)&gt;0,C6/SUM($C$2:$C$9),0)</f>
+        <v/>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>31000</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>248</v>
+      </c>
+      <c r="G6" s="15">
+        <f>IF(N(E6)&gt;0,F6/E6,"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I6" s="15">
+        <f>IF(N(E6)&gt;0,C6/E6,"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="19" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/commercial-epoxy-flooring/</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>312</v>
+      </c>
+      <c r="D7" s="15">
+        <f>IF(SUM($C$2:$C$9)&gt;0,C7/SUM($C$2:$C$9),0)</f>
+        <v/>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>2600</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="G7" s="15">
+        <f>IF(N(E7)&gt;0,F7/E7,"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I7" s="15">
+        <f>IF(N(E7)&gt;0,C7/E7,"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="19" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/blog/epoxy-vs-polished-concrete/</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>286</v>
+      </c>
+      <c r="D8" s="15">
+        <f>IF(SUM($C$2:$C$9)&gt;0,C8/SUM($C$2:$C$9),0)</f>
+        <v/>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G8" s="15">
+        <f>IF(N(E8)&gt;0,F8/E8,"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I8" s="15">
+        <f>IF(N(E8)&gt;0,C8/E8,"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="19" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/blog/diy-epoxy-vs-professional/</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>270</v>
+      </c>
+      <c r="D9" s="15">
+        <f>IF(SUM($C$2:$C$9)&gt;0,C9/SUM($C$2:$C$9),0)</f>
+        <v/>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G9" s="15">
+        <f>IF(N(E9)&gt;0,F9/E9,"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I9" s="15">
+        <f>IF(N(E9)&gt;0,C9/E9,"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="19" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J9"/>
+  <conditionalFormatting sqref="C2:C9">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00A78BFA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00A78BFA"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5463,7 +6386,7 @@
           <t>Long prompt (10+ words)</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>^\S+(\s+\S+){9,}$</t>
         </is>
@@ -5486,15 +6409,15 @@
         </is>
       </c>
       <c r="H5" s="11">
-        <f>COUNTIFS('AI Queries'!$F$2:$F$59,"*"&amp;A5&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>COUNTIFS('AI Queries'!$F$2:$F$66,"*"&amp;A5&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="I5" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$F$2:$F$59,"*"&amp;A5&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$F$2:$F$66,"*"&amp;A5&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="J5" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$F$2:$F$59,"*"&amp;A5&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$F$2:$F$66,"*"&amp;A5&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -5509,7 +6432,7 @@
           <t>Conversational length (7-9 words)</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>^\S+(\s+\S+){6,8}$</t>
         </is>
@@ -5532,15 +6455,15 @@
         </is>
       </c>
       <c r="H6" s="11">
-        <f>COUNTIFS('AI Queries'!$F$2:$F$59,"*"&amp;A6&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>COUNTIFS('AI Queries'!$F$2:$F$66,"*"&amp;A6&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="I6" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$F$2:$F$59,"*"&amp;A6&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$F$2:$F$66,"*"&amp;A6&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="J6" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$F$2:$F$59,"*"&amp;A6&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$F$2:$F$66,"*"&amp;A6&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -5555,7 +6478,7 @@
           <t>Question opener</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>(?i)^(who|whom|whose|what|whats|what's|when|where|why|how|which|is|are|was|were|am|can|could|should|would|will|do|does|did|has|have)\s</t>
         </is>
@@ -5578,15 +6501,15 @@
         </is>
       </c>
       <c r="H7" s="11">
-        <f>COUNTIFS('AI Queries'!$F$2:$F$59,"*"&amp;A7&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>COUNTIFS('AI Queries'!$F$2:$F$66,"*"&amp;A7&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="I7" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$F$2:$F$59,"*"&amp;A7&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$F$2:$F$66,"*"&amp;A7&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="J7" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$F$2:$F$59,"*"&amp;A7&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$F$2:$F$66,"*"&amp;A7&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -5601,7 +6524,7 @@
           <t>Instruction / request</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>(?i)^(give|show|tell|help|explain|list|compare|recommend|suggest|find|create|write|generate|make|summarise|summarize|describe|plan|calculate|teach|guide|walk|act|pretend|please|i need|i want|im looking|i'm looking|i am looking|looking for|can you|could you)\b</t>
         </is>
@@ -5624,15 +6547,15 @@
         </is>
       </c>
       <c r="H8" s="11">
-        <f>COUNTIFS('AI Queries'!$F$2:$F$59,"*"&amp;A8&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>COUNTIFS('AI Queries'!$F$2:$F$66,"*"&amp;A8&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="I8" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$F$2:$F$59,"*"&amp;A8&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$F$2:$F$66,"*"&amp;A8&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="J8" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$F$2:$F$59,"*"&amp;A8&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$F$2:$F$66,"*"&amp;A8&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -5647,9 +6570,9 @@
           <t>First-person context</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>(?i)\b(i|im|i'm|ive|i've|my|me|we|our|mine)\b</t>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>(?i)\b(i|im|i'm|ive|i've|my|we|our)\b</t>
         </is>
       </c>
       <c r="D9" s="11">
@@ -5666,19 +6589,19 @@
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Personal situations people describe to an AI: my garage, I have, we need, our team...</t>
+          <t>Personal situations people describe to an AI: my garage, I have, we need, our team... ('me' is left out on purpose: it would catch every 'near me' search).</t>
         </is>
       </c>
       <c r="H9" s="11">
-        <f>COUNTIFS('AI Queries'!$F$2:$F$59,"*"&amp;A9&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>COUNTIFS('AI Queries'!$F$2:$F$66,"*"&amp;A9&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="I9" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$F$2:$F$59,"*"&amp;A9&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$F$2:$F$66,"*"&amp;A9&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="J9" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$F$2:$F$59,"*"&amp;A9&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$F$2:$F$66,"*"&amp;A9&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -5693,7 +6616,7 @@
           <t>Comparison</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>(?i)\b(vs|versus|compare|compared|comparison|alternative|alternatives|difference between|differences between|better than|pros and cons|which is better)\b</t>
         </is>
@@ -5716,15 +6639,15 @@
         </is>
       </c>
       <c r="H10" s="11">
-        <f>COUNTIFS('AI Queries'!$F$2:$F$59,"*"&amp;A10&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>COUNTIFS('AI Queries'!$F$2:$F$66,"*"&amp;A10&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="I10" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$F$2:$F$59,"*"&amp;A10&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$F$2:$F$66,"*"&amp;A10&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="J10" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$F$2:$F$59,"*"&amp;A10&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$F$2:$F$66,"*"&amp;A10&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -5739,7 +6662,7 @@
           <t>Recommendation / best-of</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>(?i)\b(best|top \d+|top rated|recommend|recommended|most reliable|most popular|most affordable|cheapest|worth it|should i (buy|use|choose|get|hire|go with))\b</t>
         </is>
@@ -5762,15 +6685,15 @@
         </is>
       </c>
       <c r="H11" s="11">
-        <f>COUNTIFS('AI Queries'!$F$2:$F$59,"*"&amp;A11&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>COUNTIFS('AI Queries'!$F$2:$F$66,"*"&amp;A11&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="I11" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$F$2:$F$59,"*"&amp;A11&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$F$2:$F$66,"*"&amp;A11&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="J11" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$F$2:$F$59,"*"&amp;A11&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$F$2:$F$66,"*"&amp;A11&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -5785,7 +6708,7 @@
           <t>Constraints &amp; specifics</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>(?i)\b(for beginners|for a small|for small|for my|for someone|step by step|under \$?\d+|less than|on a budget|without|checklist|template|example|examples|in 20\d\d|for 20\d\d)\b</t>
         </is>
@@ -5808,15 +6731,15 @@
         </is>
       </c>
       <c r="H12" s="11">
-        <f>COUNTIFS('AI Queries'!$F$2:$F$59,"*"&amp;A12&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>COUNTIFS('AI Queries'!$F$2:$F$66,"*"&amp;A12&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="I12" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$F$2:$F$59,"*"&amp;A12&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$F$2:$F$66,"*"&amp;A12&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="J12" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$F$2:$F$59,"*"&amp;A12&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$F$2:$F$66,"*"&amp;A12&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -5831,7 +6754,7 @@
           <t>How / why / is-it reasoning</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>(?i)\b(how (to|do|does|can|long|much|many|often)|why (is|do|does|are|would)|what (is|are|does|happens|should)|is it (safe|worth|possible|legal|true|normal|ok|okay|better)|does it|can i|should i|do i need)\b</t>
         </is>
@@ -5854,15 +6777,15 @@
         </is>
       </c>
       <c r="H13" s="11">
-        <f>COUNTIFS('AI Queries'!$F$2:$F$59,"*"&amp;A13&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>COUNTIFS('AI Queries'!$F$2:$F$66,"*"&amp;A13&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="I13" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$F$2:$F$59,"*"&amp;A13&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$F$2:$F$66,"*"&amp;A13&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="J13" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$F$2:$F$59,"*"&amp;A13&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$F$2:$F$66,"*"&amp;A13&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -5877,9 +6800,9 @@
           <t>AI tool mention / leaked prompt</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>(?i)(chatgpt|chat gpt|openai|gpt-?[0-9]|gemini|claude|perplexity|copilot|ai overview|ai mode|\bllm\b|https?://|www\.|\.com/)</t>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>(?i)(chatgpt|chat gpt|openai|gpt-?[0-9]|gemini|claude|perplexity|copilot|ai overview|ai mode|\bllm\b|https?:?\s?//|www\.|\.com/)</t>
         </is>
       </c>
       <c r="D14" s="11">
@@ -5896,73 +6819,165 @@
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>Queries naming an AI tool, or URL-prefixed prompts like the ChatGPT queries reported leaking into GSC in late 2025.</t>
+          <t>Queries naming an AI tool, or URL-prefixed prompts (including 'https //' without the colon) like the ChatGPT queries reported leaking into GSC in late 2025.</t>
         </is>
       </c>
       <c r="H14" s="11">
-        <f>COUNTIFS('AI Queries'!$F$2:$F$59,"*"&amp;A14&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>COUNTIFS('AI Queries'!$F$2:$F$66,"*"&amp;A14&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="I14" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$F$2:$F$59,"*"&amp;A14&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$F$2:$F$66,"*"&amp;A14&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="J14" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$F$2:$F$59,"*"&amp;A14&amp;"*",'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$F$2:$F$66,"*"&amp;A14&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Follow-up / context-less prompt</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>(?i)(^(how about|what about|and what|show (me )?(photos|pics|pictures|images|designs|examples?|an example)|show (photos|pics|pictures|images)|can (you|i) (see|show)|give (me )?(images|pics|photos|examples)|which (is|one|more)|are they|is it|is that|what if|why does it|how much (would|approximately|to get)|whats? the (cheapest|cost|best))\b|\?$)</t>
+        </is>
+      </c>
+      <c r="D15" s="11">
+        <f>LEN(C15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>AI Mode follow-ups typed mid-conversation, often with no topic word at all: show me photos, which is cheaper?, how about in brisbane, are they slippery, give images of each. Also any query ending in '?'.</t>
+        </is>
+      </c>
+      <c r="H15" s="11">
+        <f>COUNTIFS('AI Queries'!$F$2:$F$66,"*"&amp;A15&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="I15" s="12">
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$F$2:$F$66,"*"&amp;A15&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="J15" s="11">
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$F$2:$F$66,"*"&amp;A15&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Search operators (AI agents &amp; tools)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>(?i)(\bsite:|\bintitle:|\binurl:|\bfiletype:|\s-site:|^\"[^\"]+\"|\s-\"[^\"]+\")</t>
+        </is>
+      </c>
+      <c r="D16" s="11">
+        <f>LEN(C16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>Queries using site:, intitle:, inurl:, -site: exclusions or a quoted phrase - typed by AI agents and research tools, not people. Reported separately and kept out of the content plan.</t>
+        </is>
+      </c>
+      <c r="H16" s="11">
+        <f>COUNTIFS('AI Queries'!$F$2:$F$66,"*"&amp;A16&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="I16" s="12">
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$F$2:$F$66,"*"&amp;A16&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="J16" s="11">
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$F$2:$F$66,"*"&amp;A16&amp;"*",'AI Queries'!$C$2:$C$66,"Yes")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>MASTER</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>Master regex (paste this first)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>(?i)^\S+(\s+\S+){9,}$|^\S+(\s+\S+){6,8}$|^(who|whom|whose|what|whats|what's|when|where|why|how|which|is|are|was|were|am|can|could|should|would|will|do|does|did|has|have)\s|^(give|show|tell|help|explain|list|compare|recommend|suggest|find|create|write|generate|make|summarise|summarize|describe|plan|calculate|teach|guide|walk|act|pretend|please|i need|i want|im looking|i'm looking|i am looking|looking for|can you|could you)\b|\b(i|im|i'm|ive|i've|my|me|we|our|mine)\b|\b(how (to|do|does|can|long|much|many|often)|why (is|do|does|are|would)|what (is|are|does|happens|should)|is it (safe|worth|possible|legal|true|normal|ok|okay|better)|does it|can i|should i|do i need)\b|(chatgpt|chat gpt|openai|gpt-?[0-9]|gemini|claude|perplexity|copilot|ai overview|ai mode|\bllm\b|https?://|www\.|\.com/)</t>
-        </is>
-      </c>
-      <c r="D15" s="20">
-        <f>LEN(C15)</f>
-        <v/>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>(?i)^\S+(\s+\S+){9,}$|^\S+(\s+\S+){6,8}$|^(who|whom|whose|what|whats|what's|when|where|why|how|which|is|are|was|were|am|can|could|should|would|will|do|does|did|has|have)\s|^(give|show|tell|help|explain|list|compare|recommend|suggest|find|create|write|generate|make|summarise|summarize|describe|plan|calculate|teach|guide|walk|act|pretend|please|i need|i want|im looking|i'm looking|i am looking|looking for|can you|could you)\b|\b(i|im|i'm|ive|i've|my|we|our)\b|\b(how (to|do|does|can|long|much|many|often)|why (is|do|does|are|would)|what (is|are|does|happens|should)|is it (safe|worth|possible|legal|true|normal|ok|okay|better)|does it|can i|should i|do i need)\b|(chatgpt|chat gpt|openai|gpt-?[0-9]|gemini|claude|perplexity|copilot|ai overview|ai mode|\bllm\b|https?:?\s?//|www\.|\.com/)|(^(how about|what about|and what|show (me )?(photos|pics|pictures|images|designs|examples?|an example)|show (photos|pics|pictures|images)|can (you|i) (see|show)|give (me )?(images|pics|photos|examples)|which (is|one|more)|are they|is it|is that|what if|why does it|how much (would|approximately|to get)|whats? the (cheapest|cost|best))\b|\?$)|(\bsite:|\bintitle:|\binurl:|\bfiletype:|\s-site:|^\"[^\"]+\"|\s-\"[^\"]+\")</t>
+        </is>
+      </c>
+      <c r="D17" s="21">
+        <f>LEN(C17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G15" s="20" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>OR of every family marked 'in master'. Use it for the first pull; run single families to get past the 1,000-row cap.</t>
         </is>
       </c>
-      <c r="H15" s="20">
-        <f>COUNTIF('AI Queries'!$C$2:$C$59,"Yes")</f>
-        <v/>
-      </c>
-      <c r="I15" s="22">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$C$2:$C$59,"Yes")</f>
-        <v/>
-      </c>
-      <c r="J15" s="20">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$C$2:$C$59,"Yes")</f>
+      <c r="H17" s="21">
+        <f>COUNTIF('AI Queries'!$C$2:$C$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="I17" s="23">
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$C$2:$C$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="J17" s="21">
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J15"/>
-  <conditionalFormatting sqref="D5:D15">
+  <autoFilter ref="A4:J17"/>
+  <conditionalFormatting sqref="D5:D17">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>4096</formula>
     </cfRule>
@@ -5971,14 +6986,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A78BFA"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6083,24 +7098,24 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>Cost &amp; price</t>
-        </is>
-      </c>
-      <c r="C2" s="23" t="inlineStr">
+          <t>Cost &amp; price: garage</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
       <c r="D2" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A2,'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A2,'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="E2" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$H$2:$H$59,A2)</f>
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$H$2:$H$66,A2)</f>
         <v/>
       </c>
       <c r="F2" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$H$2:$H$59,A2)</f>
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$H$2:$H$66,A2)</f>
         <v/>
       </c>
       <c r="G2" s="15">
@@ -6114,11 +7129,11 @@
         <v>62</v>
       </c>
       <c r="J2" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A2,'AI Queries'!$N$2:$N$59,"Yes")</f>
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A2,'AI Queries'!$N$2:$N$66,"Yes")</f>
         <v/>
       </c>
       <c r="K2" s="11">
-        <f>SUMIFS('AI Queries'!$Q$2:$Q$59,'AI Queries'!$H$2:$H$59,A2)</f>
+        <f>SUMIFS('AI Queries'!$Q$2:$Q$66,'AI Queries'!$H$2:$H$66,A2)</f>
         <v/>
       </c>
       <c r="L2" s="11" t="inlineStr">
@@ -6131,7 +7146,11 @@
           <t>4-10 4, 11-20 2, Top 3 1, 21+ 1</t>
         </is>
       </c>
-      <c r="N2" s="11" t="inlineStr"/>
+      <c r="N2" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/epoxy-flooring-cost/</t>
+        </is>
+      </c>
       <c r="O2" s="11" t="inlineStr">
         <is>
           <t>how much does epoxy flooring cost per square metre
@@ -6153,24 +7172,24 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>How long / timing</t>
-        </is>
-      </c>
-      <c r="C3" s="23" t="inlineStr">
+          <t>How long / timing: garage</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
       <c r="D3" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A3,'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A3,'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="E3" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$H$2:$H$59,A3)</f>
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$H$2:$H$66,A3)</f>
         <v/>
       </c>
       <c r="F3" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$H$2:$H$59,A3)</f>
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$H$2:$H$66,A3)</f>
         <v/>
       </c>
       <c r="G3" s="15">
@@ -6184,11 +7203,11 @@
         <v>75</v>
       </c>
       <c r="J3" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A3,'AI Queries'!$N$2:$N$59,"Yes")</f>
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A3,'AI Queries'!$N$2:$N$66,"Yes")</f>
         <v/>
       </c>
       <c r="K3" s="11">
-        <f>SUMIFS('AI Queries'!$Q$2:$Q$59,'AI Queries'!$H$2:$H$59,A3)</f>
+        <f>SUMIFS('AI Queries'!$Q$2:$Q$66,'AI Queries'!$H$2:$H$66,A3)</f>
         <v/>
       </c>
       <c r="L3" s="11" t="inlineStr">
@@ -6219,24 +7238,24 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>Choosing &amp; comparing: company</t>
-        </is>
-      </c>
-      <c r="C4" s="23" t="inlineStr">
+          <t>Cleaning &amp; care: garage</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
       <c r="D4" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A4,'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A4,'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="E4" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$H$2:$H$59,A4)</f>
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$H$2:$H$66,A4)</f>
         <v/>
       </c>
       <c r="F4" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$H$2:$H$59,A4)</f>
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$H$2:$H$66,A4)</f>
         <v/>
       </c>
       <c r="G4" s="15">
@@ -6244,101 +7263,35 @@
         <v/>
       </c>
       <c r="H4" s="11" t="n">
-        <v>10.1</v>
+        <v>5.5</v>
       </c>
       <c r="I4" s="11" t="n">
         <v>67</v>
       </c>
       <c r="J4" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A4,'AI Queries'!$N$2:$N$59,"Yes")</f>
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A4,'AI Queries'!$N$2:$N$66,"Yes")</f>
         <v/>
       </c>
       <c r="K4" s="11">
-        <f>SUMIFS('AI Queries'!$Q$2:$Q$59,'AI Queries'!$H$2:$H$59,A4)</f>
+        <f>SUMIFS('AI Queries'!$Q$2:$Q$66,'AI Queries'!$H$2:$H$66,A4)</f>
         <v/>
       </c>
       <c r="L4" s="11" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="M4" s="11" t="inlineStr">
         <is>
-          <t>4-10 7, 11-20 2, 21+ 1</t>
-        </is>
-      </c>
-      <c r="N4" s="11" t="inlineStr"/>
+          <t>4-10 3, 11-20 2, Top 3 1</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/blog/how-to-clean-epoxy-floors/</t>
+        </is>
+      </c>
       <c r="O4" s="11" t="inlineStr">
-        <is>
-          <t>is epoxy flooring worth it for a garage
-what is the best epoxy for garage floors
-what flooring is best for a warehouse with forklifts
-what is the difference between epoxy and polyaspartic coatings
-is epoxy garage flooring worth the money or should i just paint it
-which is better flake or metallic epoxy for a garage
-what colour epoxy floor hides dirt best
-compare epoxy flooring companies on the gold coast</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Cleaning &amp; care</t>
-        </is>
-      </c>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D5" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A5,'AI Queries'!$C$2:$C$59,"Yes")</f>
-        <v/>
-      </c>
-      <c r="E5" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$H$2:$H$59,A5)</f>
-        <v/>
-      </c>
-      <c r="F5" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$H$2:$H$59,A5)</f>
-        <v/>
-      </c>
-      <c r="G5" s="15">
-        <f>IF(F5&gt;0,E5/F5,0)</f>
-        <v/>
-      </c>
-      <c r="H5" s="11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>67</v>
-      </c>
-      <c r="J5" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A5,'AI Queries'!$N$2:$N$59,"Yes")</f>
-        <v/>
-      </c>
-      <c r="K5" s="11">
-        <f>SUMIFS('AI Queries'!$Q$2:$Q$59,'AI Queries'!$H$2:$H$59,A5)</f>
-        <v/>
-      </c>
-      <c r="L5" s="11" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="M5" s="11" t="inlineStr">
-        <is>
-          <t>4-10 3, 11-20 2, Top 3 1</t>
-        </is>
-      </c>
-      <c r="N5" s="11" t="inlineStr"/>
-      <c r="O5" s="11" t="inlineStr">
         <is>
           <t>how do you clean an epoxy garage floor
 how to clean epoxy floors without making them slippery
@@ -6349,6 +7302,80 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D5" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A5,'AI Queries'!$C$2:$C$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E5" s="11">
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$H$2:$H$66,A5)</f>
+        <v/>
+      </c>
+      <c r="F5" s="12">
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$H$2:$H$66,A5)</f>
+        <v/>
+      </c>
+      <c r="G5" s="15">
+        <f>IF(F5&gt;0,E5/F5,0)</f>
+        <v/>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="J5" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A5,'AI Queries'!$N$2:$N$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="K5" s="11">
+        <f>SUMIFS('AI Queries'!$Q$2:$Q$66,'AI Queries'!$H$2:$H$66,A5)</f>
+        <v/>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="M5" s="11" t="inlineStr">
+        <is>
+          <t>4-10 4, 11-20 2, 21+ 2</t>
+        </is>
+      </c>
+      <c r="N5" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/epoxy-garage-floors/</t>
+        </is>
+      </c>
+      <c r="O5" s="11" t="inlineStr">
+        <is>
+          <t>is epoxy flooring worth it for a garage
+what is the best epoxy for garage floors
+is epoxy garage flooring worth the money or should i just paint it
+how thick should an epoxy garage floor be
+give me a checklist for preparing a garage floor for epoxy
+we are building a new home when should we epoxy the garage
+my garage floor gets wet in summer will epoxy still work
+according to ai what is the most durable garage floor coating</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
@@ -6357,24 +7384,24 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Problems &amp; fixes: concrete</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="inlineStr">
+          <t>Flake: metallic</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="D6" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A6,'AI Queries'!$C$2:$C$59,"Yes")</f>
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A6,'AI Queries'!$C$2:$C$66,"Yes")</f>
         <v/>
       </c>
       <c r="E6" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$H$2:$H$59,A6)</f>
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$H$2:$H$66,A6)</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$H$2:$H$59,A6)</f>
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$H$2:$H$66,A6)</f>
         <v/>
       </c>
       <c r="G6" s="15">
@@ -6382,31 +7409,100 @@
         <v/>
       </c>
       <c r="H6" s="11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="J6" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A6,'AI Queries'!$N$2:$N$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="K6" s="11">
+        <f>SUMIFS('AI Queries'!$Q$2:$Q$66,'AI Queries'!$H$2:$H$66,A6)</f>
+        <v/>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>Top 3 2, 4-10 1</t>
+        </is>
+      </c>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/flake-epoxy-flooring/</t>
+        </is>
+      </c>
+      <c r="O6" s="11" t="inlineStr">
+        <is>
+          <t>what is flake epoxy flooring
+which is better flake or metallic epoxy for a garage
+show me photos of flake vs metallic</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Problems &amp; fixes: concrete, garage</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D7" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A7,'AI Queries'!$C$2:$C$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E7" s="11">
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$H$2:$H$66,A7)</f>
+        <v/>
+      </c>
+      <c r="F7" s="12">
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$H$2:$H$66,A7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="15">
+        <f>IF(F7&gt;0,E7/F7,0)</f>
+        <v/>
+      </c>
+      <c r="H7" s="11" t="n">
         <v>13.9</v>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="I7" s="11" t="n">
         <v>67</v>
       </c>
-      <c r="J6" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A6,'AI Queries'!$N$2:$N$59,"Yes")</f>
-        <v/>
-      </c>
-      <c r="K6" s="11">
-        <f>SUMIFS('AI Queries'!$Q$2:$Q$59,'AI Queries'!$H$2:$H$59,A6)</f>
-        <v/>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="J7" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A7,'AI Queries'!$N$2:$N$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="K7" s="11">
+        <f>SUMIFS('AI Queries'!$Q$2:$Q$66,'AI Queries'!$H$2:$H$66,A7)</f>
+        <v/>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
         <is>
           <t>Informational</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M7" s="11" t="inlineStr">
         <is>
           <t>11-20 3, 21+ 2, 4-10 1</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr"/>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="N7" s="11" t="inlineStr"/>
+      <c r="O7" s="11" t="inlineStr">
         <is>
           <t>can you put epoxy over cracked concrete
 why does diy epoxy peel off garage floors
@@ -6417,64 +7513,136 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>T6</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Choosing &amp; comparing: companies</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D8" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A8,'AI Queries'!$C$2:$C$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E8" s="11">
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$H$2:$H$66,A8)</f>
+        <v/>
+      </c>
+      <c r="F8" s="12">
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$H$2:$H$66,A8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="15">
+        <f>IF(F8&gt;0,E8/F8,0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="J8" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A8,'AI Queries'!$N$2:$N$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="K8" s="11">
+        <f>SUMIFS('AI Queries'!$Q$2:$Q$66,'AI Queries'!$H$2:$H$66,A8)</f>
+        <v/>
+      </c>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="M8" s="11" t="inlineStr">
+        <is>
+          <t>4-10 3, 11-20 2, 21+ 1</t>
+        </is>
+      </c>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/blog/diy-epoxy-vs-professional/</t>
+        </is>
+      </c>
+      <c r="O8" s="11" t="inlineStr">
+        <is>
+          <t>what flooring is best for a warehouse with forklifts
+what is the difference between epoxy and polyaspartic coatings
+what colour epoxy floor hides dirt best
+compare epoxy flooring companies on the gold coast
+recommend a good epoxy flooring installer near southport
+https://openai.com/index/chatgpt/ best epoxy flooring company gold coast reviews</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Safety &amp; standards</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D7" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A7,'AI Queries'!$C$2:$C$59,"Yes")</f>
-        <v/>
-      </c>
-      <c r="E7" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$H$2:$H$59,A7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$H$2:$H$59,A7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="15">
-        <f>IF(F7&gt;0,E7/F7,0)</f>
-        <v/>
-      </c>
-      <c r="H7" s="11" t="n">
+      <c r="D9" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A9,'AI Queries'!$C$2:$C$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E9" s="11">
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$H$2:$H$66,A9)</f>
+        <v/>
+      </c>
+      <c r="F9" s="12">
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$H$2:$H$66,A9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="15">
+        <f>IF(F9&gt;0,E9/F9,0)</f>
+        <v/>
+      </c>
+      <c r="H9" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="I9" s="11" t="n">
         <v>46</v>
       </c>
-      <c r="J7" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A7,'AI Queries'!$N$2:$N$59,"Yes")</f>
-        <v/>
-      </c>
-      <c r="K7" s="11">
-        <f>SUMIFS('AI Queries'!$Q$2:$Q$59,'AI Queries'!$H$2:$H$59,A7)</f>
-        <v/>
-      </c>
-      <c r="L7" s="11" t="inlineStr">
+      <c r="J9" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A9,'AI Queries'!$N$2:$N$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="K9" s="11">
+        <f>SUMIFS('AI Queries'!$Q$2:$Q$66,'AI Queries'!$H$2:$H$66,A9)</f>
+        <v/>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
         <is>
           <t>Informational</t>
         </is>
       </c>
-      <c r="M7" s="11" t="inlineStr">
+      <c r="M9" s="11" t="inlineStr">
         <is>
           <t>21+ 2, 4-10 1, 11-20 1</t>
         </is>
       </c>
-      <c r="N7" s="11" t="inlineStr"/>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="N9" s="11" t="inlineStr"/>
+      <c r="O9" s="11" t="inlineStr">
         <is>
           <t>is epoxy flooring slippery when wet
 is epoxy flooring toxic once cured
@@ -6483,273 +7651,405 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>T7</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>General epoxy questions</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D8" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A8,'AI Queries'!$C$2:$C$59,"Yes")</f>
-        <v/>
-      </c>
-      <c r="E8" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$H$2:$H$59,A8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$H$2:$H$59,A8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="15">
-        <f>IF(F8&gt;0,E8/F8,0)</f>
-        <v/>
-      </c>
-      <c r="H8" s="11" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>58</v>
-      </c>
-      <c r="J8" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A8,'AI Queries'!$N$2:$N$59,"Yes")</f>
-        <v/>
-      </c>
-      <c r="K8" s="11">
-        <f>SUMIFS('AI Queries'!$Q$2:$Q$59,'AI Queries'!$H$2:$H$59,A8)</f>
-        <v/>
-      </c>
-      <c r="L8" s="11" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D10" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A10,'AI Queries'!$C$2:$C$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E10" s="11">
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$H$2:$H$66,A10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="12">
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$H$2:$H$66,A10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="15">
+        <f>IF(F10&gt;0,E10/F10,0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="J10" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A10,'AI Queries'!$N$2:$N$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="K10" s="11">
+        <f>SUMIFS('AI Queries'!$Q$2:$Q$66,'AI Queries'!$H$2:$H$66,A10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Informational</t>
         </is>
       </c>
-      <c r="M8" s="11" t="inlineStr">
-        <is>
-          <t>21+ 2, 11-20 2, 4-10 1</t>
-        </is>
-      </c>
-      <c r="N8" s="11" t="inlineStr"/>
-      <c r="O8" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>21+ 2, 4-10 1, 11-20 1</t>
+        </is>
+      </c>
+      <c r="N10" s="11" t="inlineStr"/>
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>can epoxy be applied over tiles
+what should you not use on epoxy floors
 can you epoxy a pool deck or outdoor patio
-how thick should an epoxy garage floor be
-explain the steps of applying epoxy flooring
-give me a checklist for preparing a garage floor for epoxy</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>T8</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
+explain the steps of applying epoxy flooring</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Concrete: polished</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D9" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A9,'AI Queries'!$C$2:$C$59,"Yes")</f>
-        <v/>
-      </c>
-      <c r="E9" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$H$2:$H$59,A9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$H$2:$H$59,A9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="15">
-        <f>IF(F9&gt;0,E9/F9,0)</f>
-        <v/>
-      </c>
-      <c r="H9" s="11" t="n">
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D11" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A11,'AI Queries'!$C$2:$C$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E11" s="11">
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$H$2:$H$66,A11)</f>
+        <v/>
+      </c>
+      <c r="F11" s="12">
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$H$2:$H$66,A11)</f>
+        <v/>
+      </c>
+      <c r="G11" s="15">
+        <f>IF(F11&gt;0,E11/F11,0)</f>
+        <v/>
+      </c>
+      <c r="H11" s="11" t="n">
         <v>10.9</v>
       </c>
-      <c r="I9" s="11" t="n">
+      <c r="I11" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="J9" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A9,'AI Queries'!$N$2:$N$59,"Yes")</f>
-        <v/>
-      </c>
-      <c r="K9" s="11">
-        <f>SUMIFS('AI Queries'!$Q$2:$Q$59,'AI Queries'!$H$2:$H$59,A9)</f>
-        <v/>
-      </c>
-      <c r="L9" s="11" t="inlineStr">
+      <c r="J11" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A11,'AI Queries'!$N$2:$N$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="K11" s="11">
+        <f>SUMIFS('AI Queries'!$Q$2:$Q$66,'AI Queries'!$H$2:$H$66,A11)</f>
+        <v/>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
         <is>
           <t>Commercial</t>
         </is>
       </c>
-      <c r="M9" s="11" t="inlineStr">
+      <c r="M11" s="11" t="inlineStr">
         <is>
           <t>4-10 1, 11-20 1</t>
         </is>
       </c>
-      <c r="N9" s="11" t="inlineStr"/>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/blog/epoxy-vs-polished-concrete/</t>
+        </is>
+      </c>
+      <c r="O11" s="11" t="inlineStr">
         <is>
           <t>is polished concrete better than epoxy for a home
 should i choose epoxy or polished concrete for my house in a humid climate</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>T9</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Commercial</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D10" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A10,'AI Queries'!$C$2:$C$59,"Yes")</f>
-        <v/>
-      </c>
-      <c r="E10" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$H$2:$H$59,A10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$H$2:$H$59,A10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="15">
-        <f>IF(F10&gt;0,E10/F10,0)</f>
-        <v/>
-      </c>
-      <c r="H10" s="11" t="n">
+      <c r="D12" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A12,'AI Queries'!$C$2:$C$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E12" s="11">
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$H$2:$H$66,A12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="12">
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$H$2:$H$66,A12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="15">
+        <f>IF(F12&gt;0,E12/F12,0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="I10" s="11" t="n">
+      <c r="I12" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="J10" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A10,'AI Queries'!$N$2:$N$59,"Yes")</f>
-        <v/>
-      </c>
-      <c r="K10" s="11">
-        <f>SUMIFS('AI Queries'!$Q$2:$Q$59,'AI Queries'!$H$2:$H$59,A10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="J12" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A12,'AI Queries'!$N$2:$N$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="K12" s="11">
+        <f>SUMIFS('AI Queries'!$Q$2:$Q$66,'AI Queries'!$H$2:$H$66,A12)</f>
+        <v/>
+      </c>
+      <c r="L12" s="11" t="inlineStr">
         <is>
           <t>Informational</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="M12" s="11" t="inlineStr">
         <is>
           <t>11-20 2</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr"/>
-      <c r="O10" s="11" t="inlineStr">
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/commercial-epoxy-flooring/</t>
+        </is>
+      </c>
+      <c r="O12" s="11" t="inlineStr">
         <is>
           <t>is epoxy flooring good for a commercial kitchen
 what is commercial epoxy flooring used for</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>T10</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>AI Mode follow-ups (no topic word)</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D13" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A13,'AI Queries'!$C$2:$C$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E13" s="11">
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$H$2:$H$66,A13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="12">
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$H$2:$H$66,A13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="15">
+        <f>IF(F13&gt;0,E13/F13,0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="J13" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A13,'AI Queries'!$N$2:$N$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="K13" s="11">
+        <f>SUMIFS('AI Queries'!$Q$2:$Q$66,'AI Queries'!$H$2:$H$66,A13)</f>
+        <v/>
+      </c>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>Top 3 2, 4-10 2</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr"/>
+      <c r="O13" s="11" t="inlineStr">
+        <is>
+          <t>show me photos
+which is cheaper?
+how about in brisbane
+are they slippery</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Other AI-style queries</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D11" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A11,'AI Queries'!$C$2:$C$59,"Yes")</f>
-        <v/>
-      </c>
-      <c r="E11" s="11">
-        <f>SUMIFS('AI Queries'!$I$2:$I$59,'AI Queries'!$H$2:$H$59,A11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="12">
-        <f>SUMIFS('AI Queries'!$J$2:$J$59,'AI Queries'!$H$2:$H$59,A11)</f>
-        <v/>
-      </c>
-      <c r="G11" s="15">
-        <f>IF(F11&gt;0,E11/F11,0)</f>
-        <v/>
-      </c>
-      <c r="H11" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="I11" s="11" t="n">
-        <v>61</v>
-      </c>
-      <c r="J11" s="11">
-        <f>COUNTIFS('AI Queries'!$H$2:$H$59,A11,'AI Queries'!$N$2:$N$59,"Yes")</f>
-        <v/>
-      </c>
-      <c r="K11" s="11">
-        <f>SUMIFS('AI Queries'!$Q$2:$Q$59,'AI Queries'!$H$2:$H$59,A11)</f>
-        <v/>
-      </c>
-      <c r="L11" s="11" t="inlineStr">
+      <c r="D14" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A14,'AI Queries'!$C$2:$C$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E14" s="11">
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$H$2:$H$66,A14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="12">
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$H$2:$H$66,A14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="15">
+        <f>IF(F14&gt;0,E14/F14,0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="J14" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A14,'AI Queries'!$N$2:$N$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="K14" s="11">
+        <f>SUMIFS('AI Queries'!$Q$2:$Q$66,'AI Queries'!$H$2:$H$66,A14)</f>
+        <v/>
+      </c>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>Transactional</t>
+        </is>
+      </c>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>11-20 1, 21+ 1</t>
+        </is>
+      </c>
+      <c r="N14" s="11" t="inlineStr"/>
+      <c r="O14" s="11" t="inlineStr">
+        <is>
+          <t>can i do epoxy flooring myself or should i hire a professional
+does epoxy flooring add value to a house when selling</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>AI agent &amp; tool searches (site:, intitle:, quoted)</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="D15" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A15,'AI Queries'!$C$2:$C$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E15" s="11">
+        <f>SUMIFS('AI Queries'!$I$2:$I$66,'AI Queries'!$H$2:$H$66,A15)</f>
+        <v/>
+      </c>
+      <c r="F15" s="12">
+        <f>SUMIFS('AI Queries'!$J$2:$J$66,'AI Queries'!$H$2:$H$66,A15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="15">
+        <f>IF(F15&gt;0,E15/F15,0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="J15" s="11">
+        <f>COUNTIFS('AI Queries'!$H$2:$H$66,A15,'AI Queries'!$N$2:$N$66,"Yes")</f>
+        <v/>
+      </c>
+      <c r="K15" s="11">
+        <f>SUMIFS('AI Queries'!$Q$2:$Q$66,'AI Queries'!$H$2:$H$66,A15)</f>
+        <v/>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
         <is>
           <t>Informational</t>
         </is>
       </c>
-      <c r="M11" s="11" t="inlineStr">
-        <is>
-          <t>21+ 3, 11-20 2, Top 3 1, 4-10 1</t>
-        </is>
-      </c>
-      <c r="N11" s="11" t="inlineStr"/>
-      <c r="O11" s="11" t="inlineStr">
-        <is>
-          <t>what is flake epoxy flooring
-can i do epoxy flooring myself or should i hire a professional
-what should you not use on epoxy floors
-does epoxy flooring add value to a house when selling
-we are building a new home when should we epoxy the garage
-my garage floor gets wet in summer will epoxy still work
-according to ai what is the most durable garage floor coating</t>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>4-10 2</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr"/>
+      <c r="O15" s="11" t="inlineStr">
+        <is>
+          <t>"epoxy flooring" -site:reddit.com -site:youtube.com
+site:gov.au epoxy fumes ventilation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O11"/>
-  <conditionalFormatting sqref="F2:F11">
+  <autoFilter ref="A1:O15"/>
+  <conditionalFormatting sqref="F2:F15">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6763,7 +8063,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A78BFA"/>
@@ -6983,7 +8283,7 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
@@ -7040,7 +8340,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -7097,7 +8397,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -7203,7 +8503,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -7313,7 +8613,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -7423,7 +8723,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>T8</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -7476,7 +8776,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -7529,7 +8829,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -7582,7 +8882,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -7635,7 +8935,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -7688,7 +8988,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -7851,7 +9151,7 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -7957,7 +9257,7 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -8010,7 +9310,7 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>T9</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -8063,7 +9363,7 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -8116,7 +9416,7 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T13</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -8222,7 +9522,7 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -8275,7 +9575,7 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T9</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
@@ -8328,7 +9628,7 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -8381,7 +9681,7 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
@@ -8434,7 +9734,7 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T9</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
@@ -8540,7 +9840,7 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
@@ -8593,7 +9893,7 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
@@ -8646,7 +9946,7 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
@@ -8694,17 +9994,17 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>epoxy flooring cost for a 6x6 garage with crack repair included</t>
+          <t>compare epoxy flooring companies on the gold coast</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="D36" s="12" t="n">
@@ -8718,7 +10018,7 @@
         <v/>
       </c>
       <c r="G36" s="11" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
@@ -8747,17 +10047,17 @@
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>compare epoxy flooring companies on the gold coast</t>
+          <t>epoxy flooring cost for a 6x6 garage with crack repair included</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="D37" s="12" t="n">
@@ -8771,7 +10071,7 @@
         <v/>
       </c>
       <c r="G37" s="11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
@@ -8805,7 +10105,7 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>T9</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
@@ -8858,7 +10158,7 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -8911,7 +10211,7 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T13</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -8964,7 +10264,7 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T9</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -9017,7 +10317,7 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T9</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -9065,12 +10365,12 @@
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>should i choose epoxy or polished concrete for my house in a humid climate</t>
+          <t>is metallic epoxy hard to maintain</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>T8</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
@@ -9089,7 +10389,7 @@
         <v/>
       </c>
       <c r="G43" s="11" t="n">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
@@ -9118,12 +10418,12 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>is metallic epoxy hard to maintain</t>
+          <t>should i choose epoxy or polished concrete for my house in a humid climate</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
@@ -9142,7 +10442,7 @@
         <v/>
       </c>
       <c r="G44" s="11" t="n">
-        <v>19</v>
+        <v>19.6</v>
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
@@ -9176,7 +10476,7 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
@@ -9229,7 +10529,7 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
@@ -9282,7 +10582,7 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -9388,7 +10688,7 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -9436,12 +10736,12 @@
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>does epoxy flooring meet food safety standards in australia</t>
+          <t>show me photos</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
@@ -9450,31 +10750,31 @@
         </is>
       </c>
       <c r="D50" s="12" t="n">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F50" s="15">
         <f>IF(D50&gt;0,E50/D50,0)</f>
         <v/>
       </c>
       <c r="G50" s="11" t="n">
-        <v>21.3</v>
+        <v>2</v>
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>21+</t>
+          <t>Top 3</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr"/>
       <c r="J50" s="11" t="inlineStr">
         <is>
-          <t>Content gap: new section or page</t>
+          <t>Defend &amp; get cited</t>
         </is>
       </c>
       <c r="K50" s="15" t="n">
-        <v>0.026</v>
+        <v>0.25</v>
       </c>
       <c r="L50" s="11">
         <f>MAX(0,ROUND(D50*K50-E50,0))</f>
@@ -9489,12 +10789,12 @@
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>i want a durable garage floor that looks good and is easy to clean what are my options</t>
+          <t>does epoxy flooring meet food safety standards in australia</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
@@ -9503,7 +10803,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="E51" s="11" t="n">
         <v>1</v>
@@ -9513,21 +10813,21 @@
         <v/>
       </c>
       <c r="G51" s="11" t="n">
-        <v>12.9</v>
+        <v>21.3</v>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>11-20</t>
+          <t>21+</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr"/>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Striking distance: expand + internal links</t>
+          <t>Content gap: new section or page</t>
         </is>
       </c>
       <c r="K51" s="15" t="n">
-        <v>0.055</v>
+        <v>0.026</v>
       </c>
       <c r="L51" s="11">
         <f>MAX(0,ROUND(D51*K51-E51,0))</f>
@@ -9556,14 +10856,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0034D399"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9674,10 +10974,10 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>Cost &amp; price</t>
-        </is>
-      </c>
-      <c r="C2" s="23" t="inlineStr">
+          <t>Cost &amp; price: garage</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -9692,12 +10992,12 @@
           <t>Update existing page</t>
         </is>
       </c>
-      <c r="F2" s="25" t="inlineStr">
+      <c r="F2" s="19" t="inlineStr">
         <is>
           <t>8 cost questions, 6,755 impressions, average position 7.5. 'How much does epoxy flooring cost per square metre' ranks 3rd with CTR well under the expected rate (AI Overview likely). The page shows a price table but no sentence that answers the question on its own, so the summary quotes competitors.</t>
         </is>
       </c>
-      <c r="G2" s="25" t="inlineStr">
+      <c r="G2" s="19" t="inlineStr">
         <is>
           <t>Epoxy flooring on the Gold Coast usually costs [$X-$Y] per square metre installed. A standard double garage (about 36 m²) runs [$A-$B] for a flake system. Price depends mostly on floor condition: crack repair, moisture treatment and grinding add [$C-$D]. Metallic finishes cost more than flake.</t>
         </is>
@@ -9706,7 +11006,7 @@
         <f>IF(LEN(TRIM(G2))=0,0,LEN(TRIM(G2))-LEN(SUBSTITUTE(TRIM(G2)," ",""))+1)</f>
         <v/>
       </c>
-      <c r="I2" s="25" t="inlineStr">
+      <c r="I2" s="19" t="inlineStr">
         <is>
           <t>- How much does epoxy flooring cost per square metre?
 - How much does it cost to epoxy a double garage?
@@ -9714,7 +11014,7 @@
 - What is the cheapest way to resurface a garage floor?</t>
         </is>
       </c>
-      <c r="J2" s="25" t="inlineStr">
+      <c r="J2" s="19" t="inlineStr">
         <is>
           <t>Q: Why is epoxy flooring so expensive?
 A: Most of the cost is preparation: diamond grinding, crack repair and moisture testing, then two to three coats with cure time between them. Cheap jobs skip the prep, which is why they peel.
@@ -9722,7 +11022,7 @@
 A: Concrete paint or a DIY kit costs less up front but usually lasts [1-3] years in a garage that gets driven on. A professional flake system lasts [10-15+] years.</t>
         </is>
       </c>
-      <c r="K2" s="25" t="inlineStr">
+      <c r="K2" s="19" t="inlineStr">
         <is>
           <t>| Garage size | Flake system | Metallic | Crack repair |
 | Single (18 m²) | [$] | [$] | from [$] |
@@ -9730,18 +11030,18 @@
 | Triple (54 m²) | [$] | [$] | from [$] |</t>
         </is>
       </c>
-      <c r="L2" s="25" t="inlineStr">
+      <c r="L2" s="19" t="inlineStr">
         <is>
           <t>Service, FAQPage, LocalBusiness</t>
         </is>
       </c>
-      <c r="M2" s="25" t="inlineStr">
+      <c r="M2" s="19" t="inlineStr">
         <is>
           <t>- From /epoxy-garage-floors/ with anchor 'epoxy garage floor cost'
 - From /blog/diy-epoxy-vs-professional/ with anchor 'what a professional job costs'</t>
         </is>
       </c>
-      <c r="N2" s="25" t="inlineStr">
+      <c r="N2" s="19" t="inlineStr">
         <is>
           <t>- Add a price range to the Google Business Profile services list
 - Pitch the price table to Gold Coast home-improvement roundups that AI cites for cost questions</t>
@@ -9766,10 +11066,10 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>How long / timing</t>
-        </is>
-      </c>
-      <c r="C3" s="23" t="inlineStr">
+          <t>How long / timing: garage</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -9784,12 +11084,12 @@
           <t>Update existing page</t>
         </is>
       </c>
-      <c r="F3" s="25" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>Lifespan and cure-time questions rank 2-4 (4,200 impressions) but 'how long does epoxy garage floor last' gets a small share of the clicks its position should earn: the AI Overview answers it. The page mentions durability only in a bullet list.</t>
         </is>
       </c>
-      <c r="G3" s="25" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>A professionally installed epoxy garage floor lasts [10-20] years in a Queensland home garage; DIY kits usually last [1-3]. Lifespan depends on surface preparation, coating thickness and UV exposure near the door. You can walk on a new floor after [24] hours and park a car after [72] hours.</t>
         </is>
@@ -9798,20 +11098,20 @@
         <f>IF(LEN(TRIM(G3))=0,0,LEN(TRIM(G3))-LEN(SUBSTITUTE(TRIM(G3)," ",""))+1)</f>
         <v/>
       </c>
-      <c r="I3" s="25" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>- How long does an epoxy garage floor last?
 - How long after epoxy can I drive on it?
 - How long does epoxy take to cure before parking a car?</t>
         </is>
       </c>
-      <c r="J3" s="25" t="inlineStr">
+      <c r="J3" s="19" t="inlineStr">
         <is>
           <t>Q: Does Queensland heat shorten epoxy life?
 A: Heat itself doesn't, but direct sun on standard epoxy can yellow it. A UV-stable topcoat on the first metre inside the door prevents that.</t>
         </is>
       </c>
-      <c r="K3" s="25" t="inlineStr">
+      <c r="K3" s="19" t="inlineStr">
         <is>
           <t>1. Day 0: install finished
 2. Day 1: light foot traffic
@@ -9819,17 +11119,17 @@
 4. Day 7: full chemical resistance</t>
         </is>
       </c>
-      <c r="L3" s="25" t="inlineStr">
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>Service, FAQPage</t>
         </is>
       </c>
-      <c r="M3" s="25" t="inlineStr">
+      <c r="M3" s="19" t="inlineStr">
         <is>
           <t>- From the homepage 'Garage floors' card with anchor 'how long epoxy lasts'</t>
         </is>
       </c>
-      <c r="N3" s="25" t="inlineStr">
+      <c r="N3" s="19" t="inlineStr">
         <is>
           <t>- Answer the 'how long does garage epoxy last' threads on r/AusRenovation with your real numbers</t>
         </is>
@@ -9853,53 +11153,130 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>Choosing &amp; comparing: company</t>
-        </is>
-      </c>
-      <c r="C4" s="23" t="inlineStr">
+          <t>Cleaning &amp; care: garage</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>https://www.coastlineepoxy.example/epoxy-garage-floors/</t>
+          <t>https://www.coastlineepoxy.example/blog/how-to-clean-epoxy-floors/</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>New section</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="inlineStr">
-        <is>
-          <t>Ten 'is it worth it / which is best / what's the difference' prompts with 5,840 impressions at position 10. AI answers these with shortlists and comparison tables; the site has no comparison block and the 'company' prompts show buyers asking AI to compare installers.</t>
-        </is>
-      </c>
-      <c r="G4" s="25" t="inlineStr">
-        <is>
-          <t>Epoxy is worth it for most garages that get daily car traffic: it resists oil and tyre marks, cleans in minutes and lasts [10-20] years. It's not worth it on floors with rising damp unless moisture is treated first. For the same budget, polyaspartic cures faster; polished concrete suits living areas.</t>
+          <t>Update existing page</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>Cleaning questions rank 3-8. The post is a long story before the method; AI needs the method in the first lines.</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>Clean an epoxy garage floor with a soft mop, warm water and a pH-neutral cleaner. Sweep grit first, mop, then rinse so no film is left behind. Avoid vinegar, citrus and bleach-based cleaners on a regular basis: they dull the topcoat. Lift tyre marks with a degreaser and soft brush.</t>
         </is>
       </c>
       <c r="H4" s="11">
         <f>IF(LEN(TRIM(G4))=0,0,LEN(TRIM(G4))-LEN(SUBSTITUTE(TRIM(G4)," ",""))+1)</f>
         <v/>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>- How do you clean an epoxy garage floor?
+- Can I use vinegar to clean my epoxy floor?
+- How do I remove tyre marks from epoxy?
+- What should you not use on epoxy floors?</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr"/>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>Do: soft mop, pH-neutral cleaner, rinse
+Don't: vinegar, citrus, steel wool, steam mops</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>- From /epoxy-garage-floors/ 'After care' section</t>
+        </is>
+      </c>
+      <c r="N4" s="19" t="inlineStr"/>
+      <c r="O4" s="26" t="inlineStr">
+        <is>
+          <t>Confirm which cleaners the coating supplier approves.</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/epoxy-garage-floors/</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>New section</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>Eight 'is it worth it / which is best' garage prompts with 4,230 impressions at position 7.5. AI answers these with a verdict and a comparison; the garage page has neither, so the summary quotes others.</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>Epoxy is worth it for most garages that get daily car traffic: it resists oil and tyre marks, cleans in minutes and lasts [10-20] years. It's not worth it on floors with rising damp unless moisture is treated first. For the same budget, polyaspartic cures faster; polished concrete suits living areas.</t>
+        </is>
+      </c>
+      <c r="H5" s="11">
+        <f>IF(LEN(TRIM(G5))=0,0,LEN(TRIM(G5))-LEN(SUBSTITUTE(TRIM(G5)," ",""))+1)</f>
+        <v/>
+      </c>
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>- Is epoxy flooring worth it for a garage?
 - What is the best epoxy for garage floors?
-- Epoxy vs polyaspartic: what's the difference?
-- How do I compare epoxy flooring companies on the Gold Coast?</t>
-        </is>
-      </c>
-      <c r="J4" s="25" t="inlineStr">
+- Epoxy vs paint for a garage floor: which lasts?
+- How thick should an epoxy garage floor be?</t>
+        </is>
+      </c>
+      <c r="J5" s="19" t="inlineStr">
         <is>
           <t>Q: What should I ask an epoxy installer before hiring?
 A: Ask how they prepare the slab (grinding, not acid etching), the coating thickness, the warranty in writing and for three recent local jobs you can see.</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K5" s="19" t="inlineStr">
         <is>
           <t>| | Epoxy flake | Polyaspartic | Polished concrete |
 | Lifespan | [ ] | [ ] | [ ] |
@@ -9908,102 +11285,25 @@
 | Best for | Garages | Fast turnaround | Living areas |</t>
         </is>
       </c>
-      <c r="L4" s="25" t="inlineStr">
+      <c r="L5" s="19" t="inlineStr">
         <is>
           <t>FAQPage</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M5" s="19" t="inlineStr">
         <is>
           <t>- From /blog/epoxy-vs-polished-concrete/ with anchor 'epoxy vs polyaspartic'</t>
         </is>
       </c>
-      <c r="N4" s="25" t="inlineStr">
+      <c r="N5" s="19" t="inlineStr">
         <is>
           <t>- Get onto the 'best epoxy flooring Gold Coast' lists and directories that AI cites for these prompts
 - Ask recent customers for reviews that mention garage, lifespan and price</t>
         </is>
       </c>
-      <c r="O4" s="26" t="inlineStr">
+      <c r="O5" s="26" t="inlineStr">
         <is>
           <t>Fill the comparison table with figures you can stand behind.</t>
-        </is>
-      </c>
-      <c r="P4" s="11" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Cleaning &amp; care</t>
-        </is>
-      </c>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>https://www.coastlineepoxy.example/blog/how-to-clean-epoxy-floors/</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Update existing page</t>
-        </is>
-      </c>
-      <c r="F5" s="25" t="inlineStr">
-        <is>
-          <t>Cleaning questions rank 3-8. The post is a long story before the method; AI needs the method in the first lines.</t>
-        </is>
-      </c>
-      <c r="G5" s="25" t="inlineStr">
-        <is>
-          <t>Clean an epoxy garage floor with a soft mop, warm water and a pH-neutral cleaner. Sweep grit first, mop, then rinse so no film is left behind. Avoid vinegar, citrus and bleach-based cleaners on a regular basis: they dull the topcoat. Lift tyre marks with a degreaser and soft brush.</t>
-        </is>
-      </c>
-      <c r="H5" s="11">
-        <f>IF(LEN(TRIM(G5))=0,0,LEN(TRIM(G5))-LEN(SUBSTITUTE(TRIM(G5)," ",""))+1)</f>
-        <v/>
-      </c>
-      <c r="I5" s="25" t="inlineStr">
-        <is>
-          <t>- How do you clean an epoxy garage floor?
-- Can I use vinegar to clean my epoxy floor?
-- How do I remove tyre marks from epoxy?
-- What should you not use on epoxy floors?</t>
-        </is>
-      </c>
-      <c r="J5" s="25" t="inlineStr"/>
-      <c r="K5" s="25" t="inlineStr">
-        <is>
-          <t>Do: soft mop, pH-neutral cleaner, rinse
-Don't: vinegar, citrus, steel wool, steam mops</t>
-        </is>
-      </c>
-      <c r="L5" s="25" t="inlineStr">
-        <is>
-          <t>Article</t>
-        </is>
-      </c>
-      <c r="M5" s="25" t="inlineStr">
-        <is>
-          <t>- From /epoxy-garage-floors/ 'After care' section</t>
-        </is>
-      </c>
-      <c r="N5" s="25" t="inlineStr"/>
-      <c r="O5" s="26" t="inlineStr">
-        <is>
-          <t>Confirm which cleaners the coating supplier approves.</t>
         </is>
       </c>
       <c r="P5" s="11" t="inlineStr">
@@ -10020,52 +11320,130 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Problems &amp; fixes: concrete</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="inlineStr">
+          <t>Flake: metallic</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>https://www.coastlineepoxy.example/epoxy-garage-floors/</t>
+          <t>https://www.coastlineepoxy.example/flake-epoxy-flooring/</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>New section</t>
-        </is>
-      </c>
-      <c r="F6" s="25" t="inlineStr">
-        <is>
-          <t>Crack and peeling prompts sit at position 14 on average: the site never explains crack repair or why DIY epoxy peels. Long first-person prompts ('I have cracks in my garage floor...') show real worry before buying.</t>
-        </is>
-      </c>
-      <c r="G6" s="25" t="inlineStr">
-        <is>
-          <t>Yes, epoxy can go over cracked concrete, but the cracks must be repaired first. Hairline cracks are filled with an epoxy or polyurea filler; moving cracks need a flexible joint so they don't telegraph through. Most peeling comes from skipped grinding or moisture, not the epoxy itself, so prep matters most.</t>
+          <t>Update existing page</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>Flake questions rank 2.9-9.1 and the flake page is the second most AI-shown page (1,189 AI impressions). 'What is flake epoxy flooring' ranks 2.9 with low CTR: the AI answer is summarising it.</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>Flake epoxy flooring is an epoxy base coat with coloured vinyl flakes broadcast into it and sealed under a clear topcoat. The flakes hide dust and tyre marks, add texture for grip and give a speckled stone look. It is the most popular garage finish because it is durable, forgiving and easy to clean.</t>
         </is>
       </c>
       <c r="H6" s="11">
         <f>IF(LEN(TRIM(G6))=0,0,LEN(TRIM(G6))-LEN(SUBSTITUTE(TRIM(G6)," ",""))+1)</f>
         <v/>
       </c>
-      <c r="I6" s="25" t="inlineStr">
+      <c r="I6" s="19" t="inlineStr">
+        <is>
+          <t>- What is flake epoxy flooring?
+- Flake or metallic epoxy: which is better for a garage?</t>
+        </is>
+      </c>
+      <c r="J6" s="19" t="inlineStr"/>
+      <c r="K6" s="19" t="inlineStr">
+        <is>
+          <t>| | Flake | Metallic |
+| Look | Speckled | Marble / 3D |
+| Grip | Good | Lower |
+| Hides dirt | Best | Least |
+| Price per m² | [$] | [$] |</t>
+        </is>
+      </c>
+      <c r="L6" s="19" t="inlineStr">
+        <is>
+          <t>Service, FAQPage</t>
+        </is>
+      </c>
+      <c r="M6" s="19" t="inlineStr">
+        <is>
+          <t>- From /epoxy-garage-floors/ 'Finishes' section</t>
+        </is>
+      </c>
+      <c r="N6" s="19" t="inlineStr"/>
+      <c r="O6" s="26" t="inlineStr">
+        <is>
+          <t>Confirm prices per finish.</t>
+        </is>
+      </c>
+      <c r="P6" s="11" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Problems &amp; fixes: concrete, garage</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/epoxy-garage-floors/</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>New section</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>Crack and peeling prompts sit at position 14 on average: the site never explains crack repair or why DIY epoxy peels. Long first-person prompts ('I have cracks in my garage floor...') show real worry before buying.</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>Yes, epoxy can go over cracked concrete, but the cracks must be repaired first. Hairline cracks are filled with an epoxy or polyurea filler; moving cracks need a flexible joint so they don't telegraph through. Most peeling comes from skipped grinding or moisture, not the epoxy itself, so prep matters most.</t>
+        </is>
+      </c>
+      <c r="H7" s="11">
+        <f>IF(LEN(TRIM(G7))=0,0,LEN(TRIM(G7))-LEN(SUBSTITUTE(TRIM(G7)," ",""))+1)</f>
+        <v/>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>- Can you put epoxy over cracked concrete?
 - Should I fix cracks in concrete before epoxy?
 - Why does DIY epoxy peel off garage floors?</t>
         </is>
       </c>
-      <c r="J6" s="25" t="inlineStr">
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>Q: Why is my epoxy floor peeling after one year?
 A: Usually moisture coming up through the slab or a coating applied without grinding. It can be fixed, but the failed coating must be ground off first.</t>
         </is>
       </c>
-      <c r="K6" s="25" t="inlineStr">
+      <c r="K7" s="19" t="inlineStr">
         <is>
           <t>1. Moisture test the slab
 2. Diamond grind
@@ -10075,333 +11453,520 @@
 6. UV-stable topcoat</t>
         </is>
       </c>
-      <c r="L6" s="25" t="inlineStr">
+      <c r="L7" s="19" t="inlineStr">
         <is>
           <t>HowTo-style steps as an HTML list</t>
         </is>
       </c>
-      <c r="M6" s="25" t="inlineStr">
+      <c r="M7" s="19" t="inlineStr">
         <is>
           <t>- From /blog/diy-epoxy-vs-professional/ with anchor 'how we fix cracks before coating'</t>
         </is>
       </c>
-      <c r="N6" s="25" t="inlineStr">
+      <c r="N7" s="19" t="inlineStr">
         <is>
           <t>- Before/after photos of crack repair on Google Business Profile</t>
         </is>
       </c>
-      <c r="O6" s="26" t="inlineStr">
+      <c r="O7" s="26" t="inlineStr">
         <is>
           <t>Add 2-3 real before/after photos with location and date.</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr">
+      <c r="P7" s="11" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>T6</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
+    <row r="8" ht="150" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Choosing &amp; comparing: companies</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/blog/diy-epoxy-vs-professional/</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>New section</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>Six choosing prompts (1,860 impressions, position 17.9), including 'compare epoxy flooring companies on the gold coast' and a ChatGPT-prefixed 'best epoxy flooring company gold coast reviews'. AI builds a shortlist for these; the site gives it no criteria or proof to quote.</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>When you compare epoxy flooring companies, ask four things: how they prepare the slab (diamond grinding, not acid etching), which coating system and thickness they use, what the written warranty covers, and whether you can see three recent local jobs. A lower quote usually means less preparation, which is the main reason floors fail.</t>
+        </is>
+      </c>
+      <c r="H8" s="11">
+        <f>IF(LEN(TRIM(G8))=0,0,LEN(TRIM(G8))-LEN(SUBSTITUTE(TRIM(G8)," ",""))+1)</f>
+        <v/>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>- How do I compare epoxy flooring companies?
+- Epoxy vs polyaspartic: what's the difference?
+- What colour epoxy floor hides dirt best?</t>
+        </is>
+      </c>
+      <c r="J8" s="19" t="inlineStr"/>
+      <c r="K8" s="19" t="inlineStr">
+        <is>
+          <t>Checklist: preparation method / system &amp; thickness / warranty in writing / insurance / 3 local jobs to see</t>
+        </is>
+      </c>
+      <c r="L8" s="19" t="inlineStr">
+        <is>
+          <t>FAQPage</t>
+        </is>
+      </c>
+      <c r="M8" s="19" t="inlineStr"/>
+      <c r="N8" s="19" t="inlineStr">
+        <is>
+          <t>- Get onto the local 'best epoxy flooring' lists AI cites for these prompts
+- Ask recent customers for reviews that mention preparation and warranty</t>
+        </is>
+      </c>
+      <c r="O8" s="26" t="inlineStr"/>
+      <c r="P8" s="11" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="150" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Safety &amp; standards</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>https://www.coastlineepoxy.example/flake-epoxy-flooring/</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>New section</t>
         </is>
       </c>
-      <c r="F7" s="25" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>Slip and safety questions (1,910 impressions, position 14). Commercial buyers ask about food-safety standards; nothing on the site answers them.</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>Epoxy can be slippery when wet if it has a smooth high-gloss finish. A flake system or an anti-slip additive in the topcoat gives a textured surface that grips well wet or dry. Once fully cured, epoxy is inert and not considered toxic; the fumes only matter during installation and curing.</t>
         </is>
       </c>
-      <c r="H7" s="11">
-        <f>IF(LEN(TRIM(G7))=0,0,LEN(TRIM(G7))-LEN(SUBSTITUTE(TRIM(G7)," ",""))+1)</f>
-        <v/>
-      </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="H9" s="11">
+        <f>IF(LEN(TRIM(G9))=0,0,LEN(TRIM(G9))-LEN(SUBSTITUTE(TRIM(G9)," ",""))+1)</f>
+        <v/>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>- Is epoxy flooring slippery when wet?
 - How do I make my epoxy floor less slippery?
 - Is epoxy flooring toxic once cured?</t>
         </is>
       </c>
-      <c r="J7" s="25" t="inlineStr">
+      <c r="J9" s="19" t="inlineStr">
         <is>
           <t>Q: Does epoxy flooring meet food safety standards in Australia?
 A: Some commercial systems are rated for food areas. Ask for the product's data sheet and slip rating [rating] before you buy.</t>
         </is>
       </c>
-      <c r="K7" s="25" t="inlineStr"/>
-      <c r="L7" s="25" t="inlineStr">
+      <c r="K9" s="19" t="inlineStr"/>
+      <c r="L9" s="19" t="inlineStr">
         <is>
           <t>FAQPage</t>
         </is>
       </c>
-      <c r="M7" s="25" t="inlineStr">
+      <c r="M9" s="19" t="inlineStr">
         <is>
           <t>- From /commercial-epoxy-flooring/ with anchor 'slip-resistant epoxy'</t>
         </is>
       </c>
-      <c r="N7" s="25" t="inlineStr"/>
-      <c r="O7" s="26" t="inlineStr">
+      <c r="N9" s="19" t="inlineStr"/>
+      <c r="O9" s="26" t="inlineStr">
         <is>
           <t>Confirm slip ratings and food-safety certifications for the actual products before naming them.</t>
         </is>
       </c>
-      <c r="P7" s="11" t="inlineStr">
+      <c r="P9" s="11" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="150" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>T7</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
+    <row r="10" ht="150" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>General epoxy questions</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>https://www.coastlineepoxy.example/epoxy-garage-floors/</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>New section</t>
         </is>
       </c>
-      <c r="F8" s="25" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>Application questions (over tiles, pool decks, thickness) rank 21+: the topic isn't covered anywhere.</t>
         </is>
       </c>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>Epoxy can go over tiles that are firmly bonded, once the glaze is ground back and the grout lines are filled, but tiles that move will crack the coating. Outdoor pool decks need a UV-stable, slip-resistant system rather than standard epoxy. A garage floor coating is usually [X-Y] microns thick.</t>
         </is>
       </c>
-      <c r="H8" s="11">
-        <f>IF(LEN(TRIM(G8))=0,0,LEN(TRIM(G8))-LEN(SUBSTITUTE(TRIM(G8)," ",""))+1)</f>
-        <v/>
-      </c>
-      <c r="I8" s="25" t="inlineStr">
+      <c r="H10" s="11">
+        <f>IF(LEN(TRIM(G10))=0,0,LEN(TRIM(G10))-LEN(SUBSTITUTE(TRIM(G10)," ",""))+1)</f>
+        <v/>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
         <is>
           <t>- Can epoxy be applied over tiles?
 - Can you epoxy a pool deck or outdoor patio?
 - How thick should an epoxy garage floor be?</t>
         </is>
       </c>
-      <c r="J8" s="25" t="inlineStr"/>
-      <c r="K8" s="25" t="inlineStr"/>
-      <c r="L8" s="25" t="inlineStr">
+      <c r="J10" s="19" t="inlineStr"/>
+      <c r="K10" s="19" t="inlineStr"/>
+      <c r="L10" s="19" t="inlineStr">
         <is>
           <t>FAQPage</t>
         </is>
       </c>
-      <c r="M8" s="25" t="inlineStr"/>
-      <c r="N8" s="25" t="inlineStr"/>
-      <c r="O8" s="26" t="inlineStr">
+      <c r="M10" s="19" t="inlineStr"/>
+      <c r="N10" s="19" t="inlineStr"/>
+      <c r="O10" s="26" t="inlineStr">
         <is>
           <t>Confirm the thickness range and whether the business does outdoor work at all.</t>
         </is>
       </c>
-      <c r="P8" s="11" t="inlineStr">
+      <c r="P10" s="11" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="150" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>T8</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Concrete: polished</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>https://www.coastlineepoxy.example/blog/epoxy-vs-polished-concrete/</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Update existing page</t>
         </is>
       </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>Two long comparison prompts at position 11. The post compares looks but not climate or humidity, which the prompts ask about.</t>
         </is>
       </c>
-      <c r="G9" s="25" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>For a garage, epoxy usually beats polished concrete: it seals out oil and is easier to clean. For living areas in a humid climate like the Gold Coast, polished concrete breathes better and won't trap moisture. Epoxy costs less on garages; polished concrete suits large open-plan homes and needs resealing every [X] years.</t>
         </is>
       </c>
-      <c r="H9" s="11">
-        <f>IF(LEN(TRIM(G9))=0,0,LEN(TRIM(G9))-LEN(SUBSTITUTE(TRIM(G9)," ",""))+1)</f>
-        <v/>
-      </c>
-      <c r="I9" s="25" t="inlineStr">
+      <c r="H11" s="11">
+        <f>IF(LEN(TRIM(G11))=0,0,LEN(TRIM(G11))-LEN(SUBSTITUTE(TRIM(G11)," ",""))+1)</f>
+        <v/>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>- Is polished concrete better than epoxy for a home?
 - Epoxy or polished concrete in a humid climate?</t>
         </is>
       </c>
-      <c r="J9" s="25" t="inlineStr"/>
-      <c r="K9" s="25" t="inlineStr"/>
-      <c r="L9" s="25" t="inlineStr">
+      <c r="J11" s="19" t="inlineStr"/>
+      <c r="K11" s="19" t="inlineStr"/>
+      <c r="L11" s="19" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="M9" s="25" t="inlineStr">
+      <c r="M11" s="19" t="inlineStr">
         <is>
           <t>- From /epoxy-flooring-cost/ with anchor 'epoxy vs polished concrete cost'</t>
         </is>
       </c>
-      <c r="N9" s="25" t="inlineStr"/>
-      <c r="O9" s="26" t="inlineStr">
+      <c r="N11" s="19" t="inlineStr"/>
+      <c r="O11" s="26" t="inlineStr">
         <is>
           <t>Confirm resealing interval.</t>
         </is>
       </c>
-      <c r="P9" s="11" t="inlineStr">
+      <c r="P11" s="11" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="150" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>T9</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
+    <row r="12" ht="150" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Commercial</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr"/>
-      <c r="E10" s="11" t="inlineStr"/>
-      <c r="F10" s="25" t="inlineStr"/>
-      <c r="G10" s="25" t="inlineStr"/>
-      <c r="H10" s="11">
-        <f>IF(LEN(TRIM(G10))=0,0,LEN(TRIM(G10))-LEN(SUBSTITUTE(TRIM(G10)," ",""))+1)</f>
-        <v/>
-      </c>
-      <c r="I10" s="25" t="inlineStr"/>
-      <c r="J10" s="25" t="inlineStr"/>
-      <c r="K10" s="25" t="inlineStr"/>
-      <c r="L10" s="25" t="inlineStr"/>
-      <c r="M10" s="25" t="inlineStr"/>
-      <c r="N10" s="25" t="inlineStr"/>
-      <c r="O10" s="26" t="inlineStr"/>
-      <c r="P10" s="11" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/commercial-epoxy-flooring/</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr"/>
+      <c r="F12" s="19" t="inlineStr"/>
+      <c r="G12" s="19" t="inlineStr"/>
+      <c r="H12" s="11">
+        <f>IF(LEN(TRIM(G12))=0,0,LEN(TRIM(G12))-LEN(SUBSTITUTE(TRIM(G12)," ",""))+1)</f>
+        <v/>
+      </c>
+      <c r="I12" s="19" t="inlineStr"/>
+      <c r="J12" s="19" t="inlineStr"/>
+      <c r="K12" s="19" t="inlineStr"/>
+      <c r="L12" s="19" t="inlineStr"/>
+      <c r="M12" s="19" t="inlineStr"/>
+      <c r="N12" s="19" t="inlineStr"/>
+      <c r="O12" s="26" t="inlineStr"/>
+      <c r="P12" s="11" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="150" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>T10</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
+    <row r="13" ht="150" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>AI Mode follow-ups (no topic word)</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coastlineepoxy.example/flake-epoxy-flooring/</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>New section</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>Five AI Mode follow-ups with no topic word: 'show me photos', 'which is cheaper?', 'how about in brisbane', 'are they slippery'. People are mid-conversation with Google's AI and want pictures, prices and a nearby option.</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr"/>
+      <c r="H13" s="11">
+        <f>IF(LEN(TRIM(G13))=0,0,LEN(TRIM(G13))-LEN(SUBSTITUTE(TRIM(G13)," ",""))+1)</f>
+        <v/>
+      </c>
+      <c r="I13" s="19" t="inlineStr">
+        <is>
+          <t>- Epoxy floor photos: flake, metallic and solid colour
+- Which epoxy finish is cheapest?</t>
+        </is>
+      </c>
+      <c r="J13" s="19" t="inlineStr"/>
+      <c r="K13" s="19" t="inlineStr">
+        <is>
+          <t>Gallery: 12-20 real job photos, captioned with finish, room and suburb</t>
+        </is>
+      </c>
+      <c r="L13" s="19" t="inlineStr">
+        <is>
+          <t>ImageObject</t>
+        </is>
+      </c>
+      <c r="M13" s="19" t="inlineStr">
+        <is>
+          <t>- Gallery linked from every finish page</t>
+        </is>
+      </c>
+      <c r="N13" s="19" t="inlineStr">
+        <is>
+          <t>- Same photos on the Google Business Profile</t>
+        </is>
+      </c>
+      <c r="O13" s="26" t="inlineStr">
+        <is>
+          <t>Use only your own job photos.</t>
+        </is>
+      </c>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="150" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Other AI-style queries</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr"/>
-      <c r="E11" s="11" t="inlineStr"/>
-      <c r="F11" s="25" t="inlineStr"/>
-      <c r="G11" s="25" t="inlineStr"/>
-      <c r="H11" s="11">
-        <f>IF(LEN(TRIM(G11))=0,0,LEN(TRIM(G11))-LEN(SUBSTITUTE(TRIM(G11)," ",""))+1)</f>
-        <v/>
-      </c>
-      <c r="I11" s="25" t="inlineStr"/>
-      <c r="J11" s="25" t="inlineStr"/>
-      <c r="K11" s="25" t="inlineStr"/>
-      <c r="L11" s="25" t="inlineStr"/>
-      <c r="M11" s="25" t="inlineStr"/>
-      <c r="N11" s="25" t="inlineStr"/>
-      <c r="O11" s="26" t="inlineStr"/>
-      <c r="P11" s="11" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr"/>
+      <c r="E14" s="11" t="inlineStr"/>
+      <c r="F14" s="19" t="inlineStr"/>
+      <c r="G14" s="19" t="inlineStr"/>
+      <c r="H14" s="11">
+        <f>IF(LEN(TRIM(G14))=0,0,LEN(TRIM(G14))-LEN(SUBSTITUTE(TRIM(G14)," ",""))+1)</f>
+        <v/>
+      </c>
+      <c r="I14" s="19" t="inlineStr"/>
+      <c r="J14" s="19" t="inlineStr"/>
+      <c r="K14" s="19" t="inlineStr"/>
+      <c r="L14" s="19" t="inlineStr"/>
+      <c r="M14" s="19" t="inlineStr"/>
+      <c r="N14" s="19" t="inlineStr"/>
+      <c r="O14" s="26" t="inlineStr"/>
+      <c r="P14" s="11" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
     </row>
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>AI agent &amp; tool searches (site:, intitle:, quoted)</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="19" t="inlineStr"/>
+      <c r="G15" s="19" t="inlineStr"/>
+      <c r="H15" s="11">
+        <f>IF(LEN(TRIM(G15))=0,0,LEN(TRIM(G15))-LEN(SUBSTITUTE(TRIM(G15)," ",""))+1)</f>
+        <v/>
+      </c>
+      <c r="I15" s="19" t="inlineStr"/>
+      <c r="J15" s="19" t="inlineStr"/>
+      <c r="K15" s="19" t="inlineStr"/>
+      <c r="L15" s="19" t="inlineStr"/>
+      <c r="M15" s="19" t="inlineStr"/>
+      <c r="N15" s="19" t="inlineStr"/>
+      <c r="O15" s="26" t="inlineStr"/>
+      <c r="P15" s="11" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P11"/>
-  <conditionalFormatting sqref="P2:P11">
+  <autoFilter ref="A1:P15"/>
+  <conditionalFormatting sqref="P2:P15">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H11">
+  <conditionalFormatting sqref="H2:H15">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>AND(H2&gt;0,OR(H2&lt;40,H2&gt;60))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="P2:P11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"To do,In progress,Done,Skipped"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10409,7 +11974,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0034D399"/>
@@ -10502,12 +12067,12 @@
           <t>Quick win</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>Check robots.txt and the Cloudflare bot settings: allow OAI-SearchBot, ChatGPT-User, PerplexityBot, Claude-SearchBot and Bingbot</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Blocked crawlers can't cite you; this takes 15 minutes</t>
         </is>
@@ -10541,12 +12106,12 @@
           <t>Quick win</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>Verify the site in Bing Webmaster Tools (import from GSC) and switch on IndexNow</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>Several AI assistants lean on Bing's index; IndexNow pushes every update within minutes</t>
         </is>
@@ -10580,12 +12145,12 @@
           <t>Quick win</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>Add the T1 and T2 answer blocks + question headings to the cost and garage pages, then request indexing</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Top-3 rankings with low CTR: AI answers already pull from these pages, so a quotable passage can turn rankings into citations</t>
         </is>
@@ -10619,12 +12184,12 @@
           <t>Quick win</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Rewrite the cost page title to promise the specific answer: 'Epoxy Flooring Cost Gold Coast: m² Prices + Real Jobs'</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>AIO-flagged queries need a reason to click beyond the summary</t>
         </is>
@@ -10658,12 +12223,12 @@
           <t>Quick win</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Save the master regex as a GSC filter and note this report's baseline (impressions, clicks, CTR)</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>Monthly comparison shows what moved</t>
         </is>
@@ -10697,12 +12262,12 @@
           <t>Plan</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
-        <is>
-          <t>Publish the full plans for T3-T6: comparison table, crack-repair steps, safety section, FAQ blocks with schema</t>
-        </is>
-      </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>Publish the full plans for T3-T8: cleaning, garage verdict, flake vs metallic table, crack-repair steps, choosing checklist, safety section</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>AI-style impressions on those pages; position of the top query per topic</t>
         </is>
@@ -10736,12 +12301,12 @@
           <t>Plan</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>Outreach to the 'best epoxy flooring Gold Coast' lists and directories that AI cites for T3 prompts</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Number of cited sources that mention the brand</t>
         </is>
@@ -10775,12 +12340,12 @@
           <t>Plan</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
-        <is>
-          <t>Monthly prompt check: ask the top query of T1-T3 in ChatGPT, Perplexity, Gemini and Google AI Mode; log who is cited</t>
-        </is>
-      </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>Monthly prompt check: ask the top query of T1, T2 and T4 in ChatGPT, Perplexity, Gemini and Google AI Mode; log who is cited</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>Cited yes/no per platform</t>
         </is>
@@ -10814,12 +12379,12 @@
           <t>Plan</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>Publish a small price survey: 'What 50 Gold Coast garage floors actually cost' from your own jobs</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>Backlinks and citations to the survey</t>
         </is>
@@ -10853,12 +12418,12 @@
           <t>Plan</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Re-pull the master regex in GSC, compare with this baseline and move effort to the topics that grew</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>AI-style clicks and CTR vs baseline</t>
         </is>
@@ -10920,7 +12485,7 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Prompt log: top query of T1-T3 asked monthly in ChatGPT, Perplexity, Gemini and AI Mode - cited yes/no, competitors cited</t>
+          <t>Prompt log: top query of T1, T2, T4 asked monthly in ChatGPT, Perplexity, Gemini and AI Mode - cited yes/no, competitors cited</t>
         </is>
       </c>
     </row>
@@ -10962,14 +12527,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006B7280"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -11021,7 +12586,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -11151,6 +12716,30 @@
       <c r="B17" s="9" t="inlineStr">
         <is>
           <t>The GSC interface shows up to 1,000 rows per table. Run single regex families, or the API, for the full long tail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>AI Feature Pages</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>From GSC &gt; Performance &gt; Generative AI features (Beta): impressions where a page appeared in AI Overviews / AI Mode. By page, not by query. Page rows add up to more than the report total because one AI answer can show several of your pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>Follow-ups &amp; agents</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Follow-ups: short prompts with no topic word ('show me photos', 'which is cheaper?') typed inside an AI conversation. Agent searches: site:/intitle:/quoted queries from AI tools; reported, not optimised for.</t>
         </is>
       </c>
     </row>

--- a/examples/sample-report.xlsx
+++ b/examples/sample-report.xlsx
@@ -11340,7 +11340,7 @@
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>Flake questions rank 2.9-9.1 and the flake page is the second most AI-shown page (1,189 AI impressions). 'What is flake epoxy flooring' ranks 2.9 with low CTR: the AI answer is summarising it.</t>
+          <t>Flake questions rank 2.5-9.1 and the flake page is the second most AI-shown page (1,189 AI impressions). 'What is flake epoxy flooring' ranks 2.9 with low CTR: the AI answer is summarising it.</t>
         </is>
       </c>
       <c r="G6" s="19" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>Five AI Mode follow-ups with no topic word: 'show me photos', 'which is cheaper?', 'how about in brisbane', 'are they slippery'. People are mid-conversation with Google's AI and want pictures, prices and a nearby option.</t>
+          <t>Four AI Mode follow-ups with no topic word: 'show me photos', 'which is cheaper?', 'how about in brisbane', 'are they slippery'. People are mid-conversation with Google's AI and want pictures, prices and a nearby option.</t>
         </is>
       </c>
       <c r="G13" s="19" t="inlineStr"/>
